--- a/docs/mhlw/phase4_v08/001082795.xlsx
+++ b/docs/mhlw/phase4_v08/001082795.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0A31A6-070D-7545-8359-5F241CA6FE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A879F8E3-46FF-7045-AA0C-34022458FE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="付属2(健診項目一覧)" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'付属2(健診項目一覧)'!$A:$X</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'付属2(健診項目一覧)'!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -4597,22 +4599,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4704,9 +4706,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4744,7 +4746,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4850,7 +4852,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4992,7 +4994,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5000,7 +5002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z331"/>
@@ -5287,10 +5289,10 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" spans="1:24" ht="33" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C6" s="6">
@@ -5344,9 +5346,9 @@
       <c r="W6" s="6"/>
       <c r="X6" s="7"/>
     </row>
-    <row r="7" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
+    <row r="7" spans="1:24" ht="33" customHeight="1">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="6">
         <v>10</v>
       </c>
@@ -5402,9 +5404,9 @@
       <c r="W7" s="6"/>
       <c r="X7" s="7"/>
     </row>
-    <row r="8" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
+    <row r="8" spans="1:24" ht="33" customHeight="1">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="6">
         <v>10</v>
       </c>
@@ -5460,9 +5462,9 @@
       <c r="W8" s="6"/>
       <c r="X8" s="7"/>
     </row>
-    <row r="9" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
+    <row r="9" spans="1:24" ht="33" customHeight="1">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="6">
         <v>10</v>
       </c>
@@ -5520,7 +5522,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="10" spans="1:24" ht="33" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="18"/>
       <c r="C10" s="6">
@@ -5574,7 +5576,7 @@
       <c r="W10" s="6"/>
       <c r="X10" s="7"/>
     </row>
-    <row r="11" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="11" spans="1:24" ht="33" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="18"/>
       <c r="C11" s="6">
@@ -5958,7 +5960,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="18" spans="1:24" ht="33" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="18"/>
       <c r="C18" s="6">
@@ -6006,7 +6008,7 @@
       <c r="W18" s="6"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="19" spans="1:24" ht="33" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="18"/>
       <c r="C19" s="6">
@@ -6054,7 +6056,7 @@
       <c r="W19" s="6"/>
       <c r="X19" s="7"/>
     </row>
-    <row r="20" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="20" spans="1:24" ht="33" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="18"/>
       <c r="C20" s="6">
@@ -6102,7 +6104,7 @@
       <c r="W20" s="6"/>
       <c r="X20" s="7"/>
     </row>
-    <row r="21" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="21" spans="1:24" ht="33" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="18"/>
       <c r="C21" s="6">
@@ -6150,7 +6152,7 @@
       <c r="W21" s="6"/>
       <c r="X21" s="7"/>
     </row>
-    <row r="22" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="22" spans="1:24" ht="33" customHeight="1">
       <c r="A22" s="6"/>
       <c r="B22" s="18"/>
       <c r="C22" s="6">
@@ -6205,10 +6207,10 @@
       <c r="X22" s="7"/>
     </row>
     <row r="23" spans="1:24" ht="33" customHeight="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C23" s="6">
@@ -6268,9 +6270,9 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
+    <row r="24" spans="1:24" ht="33" customHeight="1">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="6">
         <v>30</v>
       </c>
@@ -6326,9 +6328,9 @@
       <c r="W24" s="6"/>
       <c r="X24" s="7"/>
     </row>
-    <row r="25" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
+    <row r="25" spans="1:24" ht="33" customHeight="1">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
       <c r="C25" s="6">
         <v>30</v>
       </c>
@@ -6385,10 +6387,10 @@
       <c r="X25" s="7"/>
     </row>
     <row r="26" spans="1:24" ht="33" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C26" s="6">
@@ -6448,9 +6450,9 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
+    <row r="27" spans="1:24" ht="33" customHeight="1">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="6">
         <v>30</v>
       </c>
@@ -6506,9 +6508,9 @@
       <c r="W27" s="6"/>
       <c r="X27" s="7"/>
     </row>
-    <row r="28" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
+    <row r="28" spans="1:24" ht="33" customHeight="1">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
       <c r="C28" s="6">
         <v>30</v>
       </c>
@@ -6564,7 +6566,7 @@
       <c r="W28" s="6"/>
       <c r="X28" s="7"/>
     </row>
-    <row r="29" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="29" spans="1:24" ht="33" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="18"/>
       <c r="C29" s="6">
@@ -6676,8 +6678,8 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A31" s="26"/>
+    <row r="31" spans="1:24" ht="33" customHeight="1">
+      <c r="A31" s="23"/>
       <c r="B31" s="18"/>
       <c r="C31" s="6">
         <v>50</v>
@@ -6734,8 +6736,8 @@
       <c r="W31" s="6"/>
       <c r="X31" s="7"/>
     </row>
-    <row r="32" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A32" s="28"/>
+    <row r="32" spans="1:24" ht="33" customHeight="1">
+      <c r="A32" s="24"/>
       <c r="B32" s="18"/>
       <c r="C32" s="6">
         <v>50</v>
@@ -6792,8 +6794,8 @@
       <c r="W32" s="6"/>
       <c r="X32" s="7"/>
     </row>
-    <row r="33" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A33" s="27"/>
+    <row r="33" spans="1:24" ht="33" customHeight="1">
+      <c r="A33" s="25"/>
       <c r="B33" s="18"/>
       <c r="C33" s="6">
         <v>50</v>
@@ -6851,10 +6853,10 @@
       <c r="X33" s="7"/>
     </row>
     <row r="34" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="23" t="s">
         <v>1132</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="23" t="s">
         <v>1132</v>
       </c>
       <c r="C34" s="6">
@@ -6912,13 +6914,13 @@
       <c r="W34" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X34" s="23" t="s">
+      <c r="X34" s="26" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="8" customFormat="1" ht="42" hidden="1" customHeight="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
+    <row r="35" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
       <c r="C35" s="6">
         <v>50</v>
       </c>
@@ -6974,11 +6976,11 @@
       <c r="W35" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X35" s="24"/>
-    </row>
-    <row r="36" spans="1:24" s="8" customFormat="1" ht="42" hidden="1" customHeight="1">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
+      <c r="X35" s="28"/>
+    </row>
+    <row r="36" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1">
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
       <c r="C36" s="6">
         <v>50</v>
       </c>
@@ -7034,13 +7036,13 @@
       <c r="W36" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X36" s="25"/>
+      <c r="X36" s="27"/>
     </row>
     <row r="37" spans="1:24" ht="42" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="23" t="s">
         <v>1132</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="23" t="s">
         <v>1132</v>
       </c>
       <c r="C37" s="6">
@@ -7098,13 +7100,13 @@
       <c r="W37" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="X37" s="23" t="s">
+      <c r="X37" s="26" t="s">
         <v>1254</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="42" hidden="1" customHeight="1">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
+    <row r="38" spans="1:24" ht="42" customHeight="1">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="6">
         <v>50</v>
       </c>
@@ -7160,11 +7162,11 @@
       <c r="W38" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="X38" s="24"/>
-    </row>
-    <row r="39" spans="1:24" ht="42" hidden="1" customHeight="1">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
+      <c r="X38" s="28"/>
+    </row>
+    <row r="39" spans="1:24" ht="42" customHeight="1">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
       <c r="C39" s="6">
         <v>50</v>
       </c>
@@ -7220,13 +7222,13 @@
       <c r="W39" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="X39" s="25"/>
+      <c r="X39" s="27"/>
     </row>
     <row r="40" spans="1:24" ht="33" customHeight="1">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C40" s="6">
@@ -7284,9 +7286,9 @@
       <c r="W40" s="6"/>
       <c r="X40" s="7"/>
     </row>
-    <row r="41" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
+    <row r="41" spans="1:24" ht="33" customHeight="1">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="6">
         <v>50</v>
       </c>
@@ -7342,9 +7344,9 @@
       <c r="W41" s="6"/>
       <c r="X41" s="7"/>
     </row>
-    <row r="42" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
+    <row r="42" spans="1:24" ht="33" customHeight="1">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
       <c r="C42" s="6">
         <v>50</v>
       </c>
@@ -7401,10 +7403,10 @@
       <c r="X42" s="7"/>
     </row>
     <row r="43" spans="1:24" ht="33" customHeight="1">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C43" s="6">
@@ -7462,9 +7464,9 @@
       <c r="W43" s="6"/>
       <c r="X43" s="7"/>
     </row>
-    <row r="44" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
+    <row r="44" spans="1:24" ht="33" customHeight="1">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="6">
         <v>50</v>
       </c>
@@ -7520,9 +7522,9 @@
       <c r="W44" s="6"/>
       <c r="X44" s="7"/>
     </row>
-    <row r="45" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
+    <row r="45" spans="1:24" ht="33" customHeight="1">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
       <c r="C45" s="6">
         <v>50</v>
       </c>
@@ -7578,9 +7580,9 @@
       <c r="W45" s="6"/>
       <c r="X45" s="7"/>
     </row>
-    <row r="46" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
+    <row r="46" spans="1:24" ht="33" customHeight="1">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
       <c r="C46" s="6">
         <v>50</v>
       </c>
@@ -7638,9 +7640,9 @@
       </c>
       <c r="X46" s="7"/>
     </row>
-    <row r="47" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
+    <row r="47" spans="1:24" ht="33" customHeight="1">
+      <c r="A47" s="25"/>
+      <c r="B47" s="25"/>
       <c r="C47" s="6">
         <v>50</v>
       </c>
@@ -7696,8 +7698,8 @@
       </c>
       <c r="X47" s="7"/>
     </row>
-    <row r="48" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A48" s="26"/>
+    <row r="48" spans="1:24" ht="33" customHeight="1">
+      <c r="A48" s="23"/>
       <c r="B48" s="18"/>
       <c r="C48" s="6">
         <v>50</v>
@@ -7754,8 +7756,8 @@
       <c r="W48" s="6"/>
       <c r="X48" s="7"/>
     </row>
-    <row r="49" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A49" s="27"/>
+    <row r="49" spans="1:24" ht="33" customHeight="1">
+      <c r="A49" s="25"/>
       <c r="B49" s="18"/>
       <c r="C49" s="6">
         <v>50</v>
@@ -7813,10 +7815,10 @@
       <c r="X49" s="7"/>
     </row>
     <row r="50" spans="1:24" ht="33" customHeight="1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C50" s="6">
@@ -7874,9 +7876,9 @@
       <c r="W50" s="6"/>
       <c r="X50" s="7"/>
     </row>
-    <row r="51" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
+    <row r="51" spans="1:24" ht="33" customHeight="1">
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
       <c r="C51" s="6">
         <v>50</v>
       </c>
@@ -7933,10 +7935,10 @@
       <c r="X51" s="7"/>
     </row>
     <row r="52" spans="1:24" ht="33" customHeight="1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C52" s="6">
@@ -7994,9 +7996,9 @@
       <c r="W52" s="6"/>
       <c r="X52" s="7"/>
     </row>
-    <row r="53" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
+    <row r="53" spans="1:24" ht="33" customHeight="1">
+      <c r="A53" s="25"/>
+      <c r="B53" s="25"/>
       <c r="C53" s="6">
         <v>50</v>
       </c>
@@ -8053,10 +8055,10 @@
       <c r="X53" s="7"/>
     </row>
     <row r="54" spans="1:24" ht="33" customHeight="1">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C54" s="6">
@@ -8114,9 +8116,9 @@
       <c r="W54" s="6"/>
       <c r="X54" s="7"/>
     </row>
-    <row r="55" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
+    <row r="55" spans="1:24" ht="33" customHeight="1">
+      <c r="A55" s="25"/>
+      <c r="B55" s="25"/>
       <c r="C55" s="6">
         <v>50</v>
       </c>
@@ -8172,8 +8174,8 @@
       <c r="W55" s="6"/>
       <c r="X55" s="7"/>
     </row>
-    <row r="56" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A56" s="26"/>
+    <row r="56" spans="1:24" ht="33" customHeight="1">
+      <c r="A56" s="23"/>
       <c r="B56" s="18"/>
       <c r="C56" s="6">
         <v>50</v>
@@ -8230,8 +8232,8 @@
       <c r="W56" s="6"/>
       <c r="X56" s="7"/>
     </row>
-    <row r="57" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A57" s="28"/>
+    <row r="57" spans="1:24" ht="33" customHeight="1">
+      <c r="A57" s="24"/>
       <c r="B57" s="18"/>
       <c r="C57" s="6">
         <v>50</v>
@@ -8290,8 +8292,8 @@
       </c>
       <c r="X57" s="7"/>
     </row>
-    <row r="58" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A58" s="27"/>
+    <row r="58" spans="1:24" ht="33" customHeight="1">
+      <c r="A58" s="25"/>
       <c r="B58" s="18"/>
       <c r="C58" s="6">
         <v>50</v>
@@ -8348,8 +8350,8 @@
       <c r="W58" s="6"/>
       <c r="X58" s="7"/>
     </row>
-    <row r="59" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A59" s="26"/>
+    <row r="59" spans="1:24" ht="33" customHeight="1">
+      <c r="A59" s="23"/>
       <c r="B59" s="18"/>
       <c r="C59" s="6">
         <v>50</v>
@@ -8408,8 +8410,8 @@
       </c>
       <c r="X59" s="7"/>
     </row>
-    <row r="60" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A60" s="28"/>
+    <row r="60" spans="1:24" ht="33" customHeight="1">
+      <c r="A60" s="24"/>
       <c r="B60" s="18"/>
       <c r="C60" s="6">
         <v>50</v>
@@ -8468,8 +8470,8 @@
       </c>
       <c r="X60" s="7"/>
     </row>
-    <row r="61" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A61" s="27"/>
+    <row r="61" spans="1:24" ht="33" customHeight="1">
+      <c r="A61" s="25"/>
       <c r="B61" s="18"/>
       <c r="C61" s="6">
         <v>50</v>
@@ -8529,10 +8531,10 @@
       <c r="X61" s="7"/>
     </row>
     <row r="62" spans="1:24" ht="33" customHeight="1">
-      <c r="A62" s="26" t="s">
+      <c r="A62" s="23" t="s">
         <v>1141</v>
       </c>
-      <c r="B62" s="26" t="s">
+      <c r="B62" s="23" t="s">
         <v>1279</v>
       </c>
       <c r="C62" s="6">
@@ -8594,9 +8596,9 @@
       <c r="W62" s="6"/>
       <c r="X62" s="7"/>
     </row>
-    <row r="63" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A63" s="27"/>
-      <c r="B63" s="27"/>
+    <row r="63" spans="1:24" ht="33" customHeight="1">
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
       <c r="C63" s="6">
         <v>50</v>
       </c>
@@ -8846,7 +8848,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="67" spans="1:24" ht="33" customHeight="1">
       <c r="A67" s="6"/>
       <c r="B67" s="18"/>
       <c r="C67" s="6">
@@ -8904,7 +8906,7 @@
       <c r="W67" s="6"/>
       <c r="X67" s="7"/>
     </row>
-    <row r="68" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="68" spans="1:24" ht="33" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="18"/>
       <c r="C68" s="6">
@@ -8962,7 +8964,7 @@
       <c r="W68" s="6"/>
       <c r="X68" s="7"/>
     </row>
-    <row r="69" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="69" spans="1:24" ht="33" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="18"/>
       <c r="C69" s="6">
@@ -9020,7 +9022,7 @@
       <c r="W69" s="6"/>
       <c r="X69" s="7"/>
     </row>
-    <row r="70" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="70" spans="1:24" ht="33" customHeight="1">
       <c r="A70" s="6"/>
       <c r="B70" s="18"/>
       <c r="C70" s="6">
@@ -9078,7 +9080,7 @@
       <c r="W70" s="6"/>
       <c r="X70" s="7"/>
     </row>
-    <row r="71" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="71" spans="1:24" ht="33" customHeight="1">
       <c r="A71" s="6"/>
       <c r="B71" s="18"/>
       <c r="C71" s="6">
@@ -9136,7 +9138,7 @@
       <c r="W71" s="6"/>
       <c r="X71" s="7"/>
     </row>
-    <row r="72" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="72" spans="1:24" ht="33" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="18"/>
       <c r="C72" s="6">
@@ -9194,7 +9196,7 @@
       <c r="W72" s="6"/>
       <c r="X72" s="7"/>
     </row>
-    <row r="73" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="73" spans="1:24" ht="33" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="18"/>
       <c r="C73" s="6">
@@ -9246,7 +9248,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="74" spans="1:24" ht="33" customHeight="1">
       <c r="A74" s="6"/>
       <c r="B74" s="18"/>
       <c r="C74" s="6">
@@ -9304,7 +9306,7 @@
       <c r="W74" s="6"/>
       <c r="X74" s="7"/>
     </row>
-    <row r="75" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="75" spans="1:24" ht="33" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="18"/>
       <c r="C75" s="6">
@@ -9363,10 +9365,10 @@
       <c r="X75" s="7"/>
     </row>
     <row r="76" spans="1:24" ht="33" customHeight="1">
-      <c r="A76" s="26" t="s">
+      <c r="A76" s="23" t="s">
         <v>1280</v>
       </c>
-      <c r="B76" s="26" t="s">
+      <c r="B76" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C76" s="6">
@@ -9422,13 +9424,13 @@
         <v>26</v>
       </c>
       <c r="W76" s="6"/>
-      <c r="X76" s="23" t="s">
+      <c r="X76" s="26" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A77" s="28"/>
-      <c r="B77" s="28"/>
+    <row r="77" spans="1:24" ht="33" customHeight="1">
+      <c r="A77" s="24"/>
+      <c r="B77" s="24"/>
       <c r="C77" s="6">
         <v>60</v>
       </c>
@@ -9482,11 +9484,11 @@
         <v>26</v>
       </c>
       <c r="W77" s="6"/>
-      <c r="X77" s="24"/>
-    </row>
-    <row r="78" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A78" s="28"/>
-      <c r="B78" s="28"/>
+      <c r="X77" s="28"/>
+    </row>
+    <row r="78" spans="1:24" ht="33" customHeight="1">
+      <c r="A78" s="24"/>
+      <c r="B78" s="24"/>
       <c r="C78" s="6">
         <v>60</v>
       </c>
@@ -9540,11 +9542,11 @@
         <v>26</v>
       </c>
       <c r="W78" s="6"/>
-      <c r="X78" s="24"/>
-    </row>
-    <row r="79" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A79" s="27"/>
-      <c r="B79" s="27"/>
+      <c r="X78" s="28"/>
+    </row>
+    <row r="79" spans="1:24" ht="33" customHeight="1">
+      <c r="A79" s="25"/>
+      <c r="B79" s="25"/>
       <c r="C79" s="6">
         <v>60</v>
       </c>
@@ -9598,13 +9600,13 @@
         <v>26</v>
       </c>
       <c r="W79" s="6"/>
-      <c r="X79" s="25"/>
+      <c r="X79" s="27"/>
     </row>
     <row r="80" spans="1:24" ht="33" customHeight="1">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="23" t="s">
         <v>1280</v>
       </c>
-      <c r="B80" s="26" t="s">
+      <c r="B80" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C80" s="6">
@@ -9660,13 +9662,13 @@
         <v>26</v>
       </c>
       <c r="W80" s="6"/>
-      <c r="X80" s="23" t="s">
+      <c r="X80" s="26" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A81" s="28"/>
-      <c r="B81" s="28"/>
+    <row r="81" spans="1:24" ht="33" customHeight="1">
+      <c r="A81" s="24"/>
+      <c r="B81" s="24"/>
       <c r="C81" s="6">
         <v>60</v>
       </c>
@@ -9720,11 +9722,11 @@
         <v>26</v>
       </c>
       <c r="W81" s="6"/>
-      <c r="X81" s="24"/>
-    </row>
-    <row r="82" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A82" s="28"/>
-      <c r="B82" s="28"/>
+      <c r="X81" s="28"/>
+    </row>
+    <row r="82" spans="1:24" ht="33" customHeight="1">
+      <c r="A82" s="24"/>
+      <c r="B82" s="24"/>
       <c r="C82" s="6">
         <v>60</v>
       </c>
@@ -9778,11 +9780,11 @@
         <v>26</v>
       </c>
       <c r="W82" s="6"/>
-      <c r="X82" s="24"/>
-    </row>
-    <row r="83" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A83" s="27"/>
-      <c r="B83" s="27"/>
+      <c r="X82" s="28"/>
+    </row>
+    <row r="83" spans="1:24" ht="33" customHeight="1">
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
       <c r="C83" s="6">
         <v>60</v>
       </c>
@@ -9836,13 +9838,13 @@
         <v>26</v>
       </c>
       <c r="W83" s="6"/>
-      <c r="X83" s="25"/>
+      <c r="X83" s="27"/>
     </row>
     <row r="84" spans="1:24" ht="33" customHeight="1">
-      <c r="A84" s="26" t="s">
+      <c r="A84" s="23" t="s">
         <v>1280</v>
       </c>
-      <c r="B84" s="26" t="s">
+      <c r="B84" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C84" s="6">
@@ -9902,9 +9904,9 @@
       </c>
       <c r="X84" s="7"/>
     </row>
-    <row r="85" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A85" s="28"/>
-      <c r="B85" s="28"/>
+    <row r="85" spans="1:24" ht="33" customHeight="1">
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
       <c r="C85" s="6">
         <v>60</v>
       </c>
@@ -9962,9 +9964,9 @@
       </c>
       <c r="X85" s="7"/>
     </row>
-    <row r="86" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A86" s="28"/>
-      <c r="B86" s="28"/>
+    <row r="86" spans="1:24" ht="33" customHeight="1">
+      <c r="A86" s="24"/>
+      <c r="B86" s="24"/>
       <c r="C86" s="6">
         <v>60</v>
       </c>
@@ -10022,9 +10024,9 @@
       </c>
       <c r="X86" s="7"/>
     </row>
-    <row r="87" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A87" s="27"/>
-      <c r="B87" s="27"/>
+    <row r="87" spans="1:24" ht="33" customHeight="1">
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
       <c r="C87" s="6">
         <v>60</v>
       </c>
@@ -10083,10 +10085,10 @@
       <c r="X87" s="7"/>
     </row>
     <row r="88" spans="1:24" ht="33" customHeight="1">
-      <c r="A88" s="26" t="s">
+      <c r="A88" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B88" s="26" t="s">
+      <c r="B88" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C88" s="6">
@@ -10140,13 +10142,13 @@
         <v>26</v>
       </c>
       <c r="W88" s="6"/>
-      <c r="X88" s="23" t="s">
+      <c r="X88" s="26" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A89" s="27"/>
-      <c r="B89" s="27"/>
+    <row r="89" spans="1:24" ht="33" customHeight="1">
+      <c r="A89" s="25"/>
+      <c r="B89" s="25"/>
       <c r="C89" s="6">
         <v>70</v>
       </c>
@@ -10198,13 +10200,13 @@
         <v>26</v>
       </c>
       <c r="W89" s="6"/>
-      <c r="X89" s="25"/>
+      <c r="X89" s="27"/>
     </row>
     <row r="90" spans="1:24" ht="33" customHeight="1">
-      <c r="A90" s="26" t="s">
+      <c r="A90" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B90" s="26" t="s">
+      <c r="B90" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C90" s="6">
@@ -10258,13 +10260,13 @@
         <v>26</v>
       </c>
       <c r="W90" s="6"/>
-      <c r="X90" s="23" t="s">
+      <c r="X90" s="26" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A91" s="27"/>
-      <c r="B91" s="27"/>
+    <row r="91" spans="1:24" ht="33" customHeight="1">
+      <c r="A91" s="25"/>
+      <c r="B91" s="25"/>
       <c r="C91" s="6">
         <v>70</v>
       </c>
@@ -10316,10 +10318,10 @@
         <v>26</v>
       </c>
       <c r="W91" s="6"/>
-      <c r="X91" s="25"/>
-    </row>
-    <row r="92" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A92" s="26"/>
+      <c r="X91" s="27"/>
+    </row>
+    <row r="92" spans="1:24" ht="33" customHeight="1">
+      <c r="A92" s="23"/>
       <c r="B92" s="18"/>
       <c r="C92" s="6">
         <v>70</v>
@@ -10372,12 +10374,12 @@
         <v>26</v>
       </c>
       <c r="W92" s="6"/>
-      <c r="X92" s="23" t="s">
+      <c r="X92" s="26" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A93" s="27"/>
+    <row r="93" spans="1:24" ht="33" customHeight="1">
+      <c r="A93" s="25"/>
       <c r="B93" s="18"/>
       <c r="C93" s="6">
         <v>70</v>
@@ -10430,9 +10432,9 @@
         <v>26</v>
       </c>
       <c r="W93" s="6"/>
-      <c r="X93" s="25"/>
-    </row>
-    <row r="94" spans="1:24" ht="33" hidden="1" customHeight="1">
+      <c r="X93" s="27"/>
+    </row>
+    <row r="94" spans="1:24" ht="33" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="18"/>
       <c r="C94" s="6">
@@ -10486,7 +10488,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="95" spans="1:24" ht="33" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="18"/>
       <c r="C95" s="6">
@@ -10536,7 +10538,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="96" spans="1:24" ht="33" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="18"/>
       <c r="C96" s="6">
@@ -10590,7 +10592,7 @@
       <c r="W96" s="6"/>
       <c r="X96" s="7"/>
     </row>
-    <row r="97" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="97" spans="1:24" ht="33" customHeight="1">
       <c r="A97" s="6"/>
       <c r="B97" s="18"/>
       <c r="C97" s="6">
@@ -10644,7 +10646,7 @@
       <c r="W97" s="6"/>
       <c r="X97" s="7"/>
     </row>
-    <row r="98" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="98" spans="1:24" ht="33" customHeight="1">
       <c r="A98" s="6"/>
       <c r="B98" s="18"/>
       <c r="C98" s="6">
@@ -10704,7 +10706,7 @@
       </c>
       <c r="X98" s="7"/>
     </row>
-    <row r="99" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="99" spans="1:24" ht="33" customHeight="1">
       <c r="A99" s="6"/>
       <c r="B99" s="18"/>
       <c r="C99" s="6">
@@ -10764,7 +10766,7 @@
       </c>
       <c r="X99" s="7"/>
     </row>
-    <row r="100" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="100" spans="1:24" ht="33" customHeight="1">
       <c r="A100" s="6"/>
       <c r="B100" s="18"/>
       <c r="C100" s="6">
@@ -10824,7 +10826,7 @@
       </c>
       <c r="X100" s="7"/>
     </row>
-    <row r="101" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="101" spans="1:24" ht="33" customHeight="1">
       <c r="A101" s="6"/>
       <c r="B101" s="18"/>
       <c r="C101" s="6">
@@ -10884,7 +10886,7 @@
       </c>
       <c r="X101" s="7"/>
     </row>
-    <row r="102" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="102" spans="1:24" ht="33" customHeight="1">
       <c r="A102" s="6"/>
       <c r="B102" s="18"/>
       <c r="C102" s="6">
@@ -10944,7 +10946,7 @@
       </c>
       <c r="X102" s="7"/>
     </row>
-    <row r="103" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="103" spans="1:24" ht="33" customHeight="1">
       <c r="A103" s="6"/>
       <c r="B103" s="18"/>
       <c r="C103" s="6">
@@ -11004,7 +11006,7 @@
       </c>
       <c r="X103" s="7"/>
     </row>
-    <row r="104" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="104" spans="1:24" ht="33" customHeight="1">
       <c r="A104" s="6"/>
       <c r="B104" s="18"/>
       <c r="C104" s="6">
@@ -11064,7 +11066,7 @@
       </c>
       <c r="X104" s="7"/>
     </row>
-    <row r="105" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="105" spans="1:24" ht="33" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="18"/>
       <c r="C105" s="6">
@@ -11374,7 +11376,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="110" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="110" spans="1:24" ht="33" customHeight="1">
       <c r="A110" s="6"/>
       <c r="B110" s="18"/>
       <c r="C110" s="6">
@@ -11434,7 +11436,7 @@
       <c r="W110" s="6"/>
       <c r="X110" s="7"/>
     </row>
-    <row r="111" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="111" spans="1:24" ht="33" customHeight="1">
       <c r="A111" s="6"/>
       <c r="B111" s="18"/>
       <c r="C111" s="6">
@@ -11494,7 +11496,7 @@
       <c r="W111" s="6"/>
       <c r="X111" s="7"/>
     </row>
-    <row r="112" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="112" spans="1:24" ht="33" customHeight="1">
       <c r="A112" s="6"/>
       <c r="B112" s="18"/>
       <c r="C112" s="6">
@@ -11554,7 +11556,7 @@
       <c r="W112" s="6"/>
       <c r="X112" s="7"/>
     </row>
-    <row r="113" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="113" spans="1:24" ht="33" customHeight="1">
       <c r="A113" s="6"/>
       <c r="B113" s="18"/>
       <c r="C113" s="6">
@@ -11614,7 +11616,7 @@
       <c r="W113" s="6"/>
       <c r="X113" s="7"/>
     </row>
-    <row r="114" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="114" spans="1:24" ht="33" customHeight="1">
       <c r="A114" s="6"/>
       <c r="B114" s="18"/>
       <c r="C114" s="6">
@@ -11916,7 +11918,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="119" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="119" spans="1:24" ht="33" customHeight="1">
       <c r="A119" s="6"/>
       <c r="B119" s="18"/>
       <c r="C119" s="6">
@@ -11978,7 +11980,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="120" spans="1:24" ht="33" customHeight="1">
       <c r="A120" s="6"/>
       <c r="B120" s="18"/>
       <c r="C120" s="6">
@@ -12040,7 +12042,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="121" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="121" spans="1:24" ht="33" customHeight="1">
       <c r="A121" s="6"/>
       <c r="B121" s="18"/>
       <c r="C121" s="6">
@@ -12098,7 +12100,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="122" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="122" spans="1:24" ht="33" customHeight="1">
       <c r="A122" s="6"/>
       <c r="B122" s="18"/>
       <c r="C122" s="6">
@@ -12156,7 +12158,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="123" spans="1:24" ht="33" customHeight="1">
       <c r="A123" s="6"/>
       <c r="B123" s="18"/>
       <c r="C123" s="6">
@@ -12212,7 +12214,7 @@
       <c r="W123" s="6"/>
       <c r="X123" s="7"/>
     </row>
-    <row r="124" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="124" spans="1:24" ht="33" customHeight="1">
       <c r="A124" s="6"/>
       <c r="B124" s="18"/>
       <c r="C124" s="6">
@@ -12274,7 +12276,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="125" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="125" spans="1:24" ht="33" customHeight="1">
       <c r="A125" s="6"/>
       <c r="B125" s="18"/>
       <c r="C125" s="6">
@@ -12336,7 +12338,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="126" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="126" spans="1:24" ht="33" customHeight="1">
       <c r="A126" s="6"/>
       <c r="B126" s="18"/>
       <c r="C126" s="6">
@@ -12394,7 +12396,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="127" spans="1:24" ht="33" customHeight="1">
       <c r="A127" s="6"/>
       <c r="B127" s="18"/>
       <c r="C127" s="6">
@@ -12452,7 +12454,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="128" spans="1:24" ht="33" customHeight="1">
       <c r="A128" s="6"/>
       <c r="B128" s="18"/>
       <c r="C128" s="6">
@@ -12508,7 +12510,7 @@
       <c r="W128" s="6"/>
       <c r="X128" s="7"/>
     </row>
-    <row r="129" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="129" spans="1:24" ht="33" customHeight="1">
       <c r="A129" s="6"/>
       <c r="B129" s="18"/>
       <c r="C129" s="6">
@@ -12562,7 +12564,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="130" spans="1:24" ht="33" customHeight="1">
       <c r="A130" s="6"/>
       <c r="B130" s="18"/>
       <c r="C130" s="6">
@@ -12612,7 +12614,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="131" spans="1:24" ht="33" customHeight="1">
       <c r="A131" s="6"/>
       <c r="B131" s="18"/>
       <c r="C131" s="6">
@@ -12666,7 +12668,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="132" spans="1:24" ht="33" customHeight="1">
       <c r="A132" s="6"/>
       <c r="B132" s="18"/>
       <c r="C132" s="6">
@@ -12720,7 +12722,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="133" spans="1:24" ht="33" customHeight="1">
       <c r="A133" s="6"/>
       <c r="B133" s="18"/>
       <c r="C133" s="6">
@@ -12774,7 +12776,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="134" spans="1:24" ht="33" customHeight="1">
       <c r="A134" s="6"/>
       <c r="B134" s="18"/>
       <c r="C134" s="6">
@@ -12832,7 +12834,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="135" spans="1:24" ht="33" customHeight="1">
       <c r="A135" s="6"/>
       <c r="B135" s="18"/>
       <c r="C135" s="6">
@@ -12890,7 +12892,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="136" spans="1:24" ht="33" customHeight="1">
       <c r="A136" s="6"/>
       <c r="B136" s="18"/>
       <c r="C136" s="6">
@@ -12944,7 +12946,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="137" spans="1:24" ht="33" customHeight="1">
       <c r="A137" s="6"/>
       <c r="B137" s="18"/>
       <c r="C137" s="6">
@@ -12998,7 +13000,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="138" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="138" spans="1:24" ht="33" customHeight="1">
       <c r="A138" s="6"/>
       <c r="B138" s="18"/>
       <c r="C138" s="6">
@@ -13050,7 +13052,7 @@
       <c r="W138" s="6"/>
       <c r="X138" s="7"/>
     </row>
-    <row r="139" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="139" spans="1:24" ht="33" customHeight="1">
       <c r="A139" s="6"/>
       <c r="B139" s="18"/>
       <c r="C139" s="6">
@@ -13108,7 +13110,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="140" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="140" spans="1:24" ht="33" customHeight="1">
       <c r="A140" s="6"/>
       <c r="B140" s="18"/>
       <c r="C140" s="6">
@@ -13162,7 +13164,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="141" spans="1:24" ht="33" customHeight="1">
       <c r="A141" s="6"/>
       <c r="B141" s="18"/>
       <c r="C141" s="6">
@@ -13216,7 +13218,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="142" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="142" spans="1:24" ht="33" customHeight="1">
       <c r="A142" s="6"/>
       <c r="B142" s="18"/>
       <c r="C142" s="6">
@@ -13268,7 +13270,7 @@
       <c r="W142" s="6"/>
       <c r="X142" s="7"/>
     </row>
-    <row r="143" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="143" spans="1:24" ht="33" customHeight="1">
       <c r="A143" s="6"/>
       <c r="B143" s="18"/>
       <c r="C143" s="6">
@@ -13326,7 +13328,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="144" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="144" spans="1:24" ht="33" customHeight="1">
       <c r="A144" s="6"/>
       <c r="B144" s="18"/>
       <c r="C144" s="6">
@@ -13380,7 +13382,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="145" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="145" spans="1:24" ht="33" customHeight="1">
       <c r="A145" s="6"/>
       <c r="B145" s="18"/>
       <c r="C145" s="6">
@@ -13434,7 +13436,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="146" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="146" spans="1:24" ht="33" customHeight="1">
       <c r="A146" s="6"/>
       <c r="B146" s="18"/>
       <c r="C146" s="6">
@@ -13486,7 +13488,7 @@
       <c r="W146" s="6"/>
       <c r="X146" s="7"/>
     </row>
-    <row r="147" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="147" spans="1:24" ht="33" customHeight="1">
       <c r="A147" s="6"/>
       <c r="B147" s="18"/>
       <c r="C147" s="6">
@@ -13540,7 +13542,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="148" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="148" spans="1:24" ht="33" customHeight="1">
       <c r="A148" s="6"/>
       <c r="B148" s="18"/>
       <c r="C148" s="6">
@@ -13590,7 +13592,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="149" spans="1:24" ht="33" customHeight="1">
       <c r="A149" s="6"/>
       <c r="B149" s="18"/>
       <c r="C149" s="6">
@@ -13646,7 +13648,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="150" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="150" spans="1:24" ht="33" customHeight="1">
       <c r="A150" s="6"/>
       <c r="B150" s="18"/>
       <c r="C150" s="6">
@@ -13700,7 +13702,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="151" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="151" spans="1:24" ht="33" customHeight="1">
       <c r="A151" s="6"/>
       <c r="B151" s="18"/>
       <c r="C151" s="6">
@@ -13750,7 +13752,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="152" spans="1:24" ht="33" customHeight="1">
       <c r="A152" s="6"/>
       <c r="B152" s="18"/>
       <c r="C152" s="6">
@@ -13804,7 +13806,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="153" spans="1:24" ht="33" customHeight="1">
       <c r="A153" s="6"/>
       <c r="B153" s="18"/>
       <c r="C153" s="6">
@@ -13854,7 +13856,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="154" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="154" spans="1:24" ht="33" customHeight="1">
       <c r="A154" s="6"/>
       <c r="B154" s="18"/>
       <c r="C154" s="6">
@@ -13908,7 +13910,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="155" spans="1:24" ht="33" customHeight="1">
       <c r="A155" s="6"/>
       <c r="B155" s="18"/>
       <c r="C155" s="6">
@@ -13958,7 +13960,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="156" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="156" spans="1:24" ht="33" customHeight="1">
       <c r="A156" s="6"/>
       <c r="B156" s="18"/>
       <c r="C156" s="6">
@@ -14012,7 +14014,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="157" spans="1:24" ht="33" customHeight="1">
       <c r="A157" s="6"/>
       <c r="B157" s="18"/>
       <c r="C157" s="6">
@@ -14062,7 +14064,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="158" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="158" spans="1:24" ht="33" customHeight="1">
       <c r="A158" s="6"/>
       <c r="B158" s="18"/>
       <c r="C158" s="6">
@@ -14116,7 +14118,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="159" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="159" spans="1:24" ht="33" customHeight="1">
       <c r="A159" s="6"/>
       <c r="B159" s="18"/>
       <c r="C159" s="6">
@@ -14166,7 +14168,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="160" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="160" spans="1:24" ht="33" customHeight="1">
       <c r="A160" s="6"/>
       <c r="B160" s="18"/>
       <c r="C160" s="6">
@@ -14220,7 +14222,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="161" spans="1:24" ht="33" customHeight="1">
       <c r="A161" s="6"/>
       <c r="B161" s="18"/>
       <c r="C161" s="6">
@@ -14270,7 +14272,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="162" spans="1:24" ht="33" customHeight="1">
       <c r="A162" s="6"/>
       <c r="B162" s="18"/>
       <c r="C162" s="6">
@@ -14324,7 +14326,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="163" spans="1:24" ht="33" customHeight="1">
       <c r="A163" s="6"/>
       <c r="B163" s="18"/>
       <c r="C163" s="6">
@@ -14374,7 +14376,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="164" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="164" spans="1:24" ht="33" customHeight="1">
       <c r="A164" s="6"/>
       <c r="B164" s="18"/>
       <c r="C164" s="6">
@@ -14428,7 +14430,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="165" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="165" spans="1:24" ht="33" customHeight="1">
       <c r="A165" s="6"/>
       <c r="B165" s="18"/>
       <c r="C165" s="6">
@@ -14484,7 +14486,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="166" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="166" spans="1:24" ht="33" customHeight="1">
       <c r="A166" s="6"/>
       <c r="B166" s="18"/>
       <c r="C166" s="6">
@@ -14538,7 +14540,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="167" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="167" spans="1:24" ht="33" customHeight="1">
       <c r="A167" s="6"/>
       <c r="B167" s="18"/>
       <c r="C167" s="6">
@@ -14592,7 +14594,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="168" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="168" spans="1:24" ht="33" customHeight="1">
       <c r="A168" s="6"/>
       <c r="B168" s="18"/>
       <c r="C168" s="6">
@@ -14642,7 +14644,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="169" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="169" spans="1:24" ht="33" customHeight="1">
       <c r="A169" s="6"/>
       <c r="B169" s="18"/>
       <c r="C169" s="6">
@@ -14696,7 +14698,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="170" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="170" spans="1:24" ht="33" customHeight="1">
       <c r="A170" s="6"/>
       <c r="B170" s="18"/>
       <c r="C170" s="6">
@@ -14746,7 +14748,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="171" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="171" spans="1:24" ht="33" customHeight="1">
       <c r="A171" s="6"/>
       <c r="B171" s="18"/>
       <c r="C171" s="6">
@@ -14802,7 +14804,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="172" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="172" spans="1:24" ht="33" customHeight="1">
       <c r="A172" s="6"/>
       <c r="B172" s="18"/>
       <c r="C172" s="6">
@@ -14858,7 +14860,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="173" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="173" spans="1:24" ht="33" customHeight="1">
       <c r="A173" s="6"/>
       <c r="B173" s="18"/>
       <c r="C173" s="6">
@@ -14912,7 +14914,7 @@
       <c r="W173" s="6"/>
       <c r="X173" s="7"/>
     </row>
-    <row r="174" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="174" spans="1:24" ht="33" customHeight="1">
       <c r="A174" s="6"/>
       <c r="B174" s="18"/>
       <c r="C174" s="6">
@@ -14966,7 +14968,7 @@
       <c r="W174" s="6"/>
       <c r="X174" s="7"/>
     </row>
-    <row r="175" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="175" spans="1:24" ht="33" customHeight="1">
       <c r="A175" s="6"/>
       <c r="B175" s="18"/>
       <c r="C175" s="6">
@@ -15020,7 +15022,7 @@
       <c r="W175" s="6"/>
       <c r="X175" s="7"/>
     </row>
-    <row r="176" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="176" spans="1:24" ht="33" customHeight="1">
       <c r="A176" s="6"/>
       <c r="B176" s="18"/>
       <c r="C176" s="6">
@@ -15074,7 +15076,7 @@
       <c r="W176" s="6"/>
       <c r="X176" s="7"/>
     </row>
-    <row r="177" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="177" spans="1:24" ht="33" customHeight="1">
       <c r="A177" s="6"/>
       <c r="B177" s="18"/>
       <c r="C177" s="6">
@@ -15124,7 +15126,7 @@
       <c r="W177" s="6"/>
       <c r="X177" s="7"/>
     </row>
-    <row r="178" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="178" spans="1:24" ht="33" customHeight="1">
       <c r="A178" s="6"/>
       <c r="B178" s="18"/>
       <c r="C178" s="6">
@@ -15174,7 +15176,7 @@
       <c r="W178" s="6"/>
       <c r="X178" s="7"/>
     </row>
-    <row r="179" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="179" spans="1:24" ht="33" customHeight="1">
       <c r="A179" s="6"/>
       <c r="B179" s="18"/>
       <c r="C179" s="6">
@@ -15224,7 +15226,7 @@
       <c r="W179" s="6"/>
       <c r="X179" s="7"/>
     </row>
-    <row r="180" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="180" spans="1:24" ht="33" customHeight="1">
       <c r="A180" s="6"/>
       <c r="B180" s="18"/>
       <c r="C180" s="6">
@@ -15274,7 +15276,7 @@
       <c r="W180" s="6"/>
       <c r="X180" s="7"/>
     </row>
-    <row r="181" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="181" spans="1:24" ht="33" customHeight="1">
       <c r="A181" s="6"/>
       <c r="B181" s="18"/>
       <c r="C181" s="6">
@@ -15328,7 +15330,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="182" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="182" spans="1:24" ht="33" customHeight="1">
       <c r="A182" s="6"/>
       <c r="B182" s="18"/>
       <c r="C182" s="6">
@@ -15382,7 +15384,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="183" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="183" spans="1:24" ht="33" customHeight="1">
       <c r="A183" s="6"/>
       <c r="B183" s="18"/>
       <c r="C183" s="6">
@@ -15436,7 +15438,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="184" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="184" spans="1:24" ht="33" customHeight="1">
       <c r="A184" s="6"/>
       <c r="B184" s="18"/>
       <c r="C184" s="6">
@@ -15490,7 +15492,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="185" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="185" spans="1:24" ht="33" customHeight="1">
       <c r="A185" s="6"/>
       <c r="B185" s="18"/>
       <c r="C185" s="6">
@@ -15544,7 +15546,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="186" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="186" spans="1:24" ht="33" customHeight="1">
       <c r="A186" s="6"/>
       <c r="B186" s="18"/>
       <c r="C186" s="6">
@@ -16148,7 +16150,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="196" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="196" spans="1:24" ht="33" customHeight="1">
       <c r="A196" s="6"/>
       <c r="B196" s="18"/>
       <c r="C196" s="6">
@@ -16202,7 +16204,7 @@
       <c r="W196" s="6"/>
       <c r="X196" s="7"/>
     </row>
-    <row r="197" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="197" spans="1:24" ht="33" customHeight="1">
       <c r="A197" s="6"/>
       <c r="B197" s="18"/>
       <c r="C197" s="6">
@@ -16256,7 +16258,7 @@
       <c r="W197" s="6"/>
       <c r="X197" s="7"/>
     </row>
-    <row r="198" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="198" spans="1:24" ht="33" customHeight="1">
       <c r="A198" s="6"/>
       <c r="B198" s="18"/>
       <c r="C198" s="6">
@@ -16314,7 +16316,7 @@
       <c r="W198" s="6"/>
       <c r="X198" s="7"/>
     </row>
-    <row r="199" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="199" spans="1:24" ht="33" customHeight="1">
       <c r="A199" s="6"/>
       <c r="B199" s="18"/>
       <c r="C199" s="6">
@@ -16372,7 +16374,7 @@
       <c r="W199" s="6"/>
       <c r="X199" s="7"/>
     </row>
-    <row r="200" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="200" spans="1:24" ht="33" customHeight="1">
       <c r="A200" s="6"/>
       <c r="B200" s="18"/>
       <c r="C200" s="6">
@@ -16430,7 +16432,7 @@
       <c r="W200" s="6"/>
       <c r="X200" s="7"/>
     </row>
-    <row r="201" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="201" spans="1:24" ht="33" customHeight="1">
       <c r="A201" s="6"/>
       <c r="B201" s="18"/>
       <c r="C201" s="6">
@@ -16488,7 +16490,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="202" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="202" spans="1:24" ht="33" customHeight="1">
       <c r="A202" s="6"/>
       <c r="B202" s="18"/>
       <c r="C202" s="6">
@@ -16546,7 +16548,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="203" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="203" spans="1:24" ht="33" customHeight="1">
       <c r="A203" s="6"/>
       <c r="B203" s="18"/>
       <c r="C203" s="6">
@@ -16604,7 +16606,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="204" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="204" spans="1:24" ht="33" customHeight="1">
       <c r="A204" s="6"/>
       <c r="B204" s="18"/>
       <c r="C204" s="6">
@@ -16662,7 +16664,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="205" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="205" spans="1:24" ht="33" customHeight="1">
       <c r="A205" s="6"/>
       <c r="B205" s="18"/>
       <c r="C205" s="6">
@@ -16718,7 +16720,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="206" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="206" spans="1:24" ht="33" customHeight="1">
       <c r="A206" s="6"/>
       <c r="B206" s="18"/>
       <c r="C206" s="6">
@@ -16774,7 +16776,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="207" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="207" spans="1:24" ht="33" customHeight="1">
       <c r="A207" s="6"/>
       <c r="B207" s="18"/>
       <c r="C207" s="6">
@@ -16830,7 +16832,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="208" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="208" spans="1:24" ht="33" customHeight="1">
       <c r="A208" s="6"/>
       <c r="B208" s="18"/>
       <c r="C208" s="6">
@@ -16886,7 +16888,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="209" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="209" spans="1:24" ht="33" customHeight="1">
       <c r="A209" s="6"/>
       <c r="B209" s="18"/>
       <c r="C209" s="6">
@@ -16942,7 +16944,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="210" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="210" spans="1:24" ht="33" customHeight="1">
       <c r="A210" s="6"/>
       <c r="B210" s="18"/>
       <c r="C210" s="6">
@@ -16998,7 +17000,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="211" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="211" spans="1:24" ht="33" customHeight="1">
       <c r="A211" s="6"/>
       <c r="B211" s="18"/>
       <c r="C211" s="6">
@@ -17052,7 +17054,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="212" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="212" spans="1:24" ht="33" customHeight="1">
       <c r="A212" s="6"/>
       <c r="B212" s="18"/>
       <c r="C212" s="6">
@@ -17100,7 +17102,7 @@
       <c r="W212" s="6"/>
       <c r="X212" s="7"/>
     </row>
-    <row r="213" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="213" spans="1:24" ht="33" customHeight="1">
       <c r="A213" s="6"/>
       <c r="B213" s="18"/>
       <c r="C213" s="6">
@@ -17148,7 +17150,7 @@
       <c r="W213" s="6"/>
       <c r="X213" s="7"/>
     </row>
-    <row r="214" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="214" spans="1:24" ht="33" customHeight="1">
       <c r="A214" s="6"/>
       <c r="B214" s="18"/>
       <c r="C214" s="6">
@@ -17426,7 +17428,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="219" spans="1:24" ht="114.75" hidden="1" customHeight="1">
+    <row r="219" spans="1:24" ht="114.75" customHeight="1">
       <c r="A219" s="6" t="s">
         <v>1131</v>
       </c>
@@ -17476,7 +17478,7 @@
       </c>
       <c r="X219" s="7"/>
     </row>
-    <row r="220" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="220" spans="1:24" ht="33" customHeight="1">
       <c r="A220" s="6"/>
       <c r="B220" s="18"/>
       <c r="C220" s="6">
@@ -17526,7 +17528,7 @@
       <c r="W220" s="6"/>
       <c r="X220" s="7"/>
     </row>
-    <row r="221" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="221" spans="1:24" ht="33" customHeight="1">
       <c r="A221" s="6"/>
       <c r="B221" s="18"/>
       <c r="C221" s="6">
@@ -17574,7 +17576,7 @@
       </c>
       <c r="X221" s="7"/>
     </row>
-    <row r="222" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="222" spans="1:24" ht="33" customHeight="1">
       <c r="A222" s="6"/>
       <c r="B222" s="18"/>
       <c r="C222" s="6">
@@ -17624,7 +17626,7 @@
       <c r="W222" s="6"/>
       <c r="X222" s="7"/>
     </row>
-    <row r="223" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="223" spans="1:24" ht="33" customHeight="1">
       <c r="A223" s="6"/>
       <c r="B223" s="18"/>
       <c r="C223" s="6">
@@ -17672,7 +17674,7 @@
       </c>
       <c r="X223" s="7"/>
     </row>
-    <row r="224" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="224" spans="1:24" ht="33" customHeight="1">
       <c r="A224" s="6"/>
       <c r="B224" s="18"/>
       <c r="C224" s="6">
@@ -17722,7 +17724,7 @@
       <c r="W224" s="6"/>
       <c r="X224" s="7"/>
     </row>
-    <row r="225" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="225" spans="1:24" ht="33" customHeight="1">
       <c r="A225" s="6"/>
       <c r="B225" s="18"/>
       <c r="C225" s="6">
@@ -17770,7 +17772,7 @@
       </c>
       <c r="X225" s="7"/>
     </row>
-    <row r="226" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="226" spans="1:24" ht="33" customHeight="1">
       <c r="A226" s="6"/>
       <c r="B226" s="18"/>
       <c r="C226" s="6">
@@ -17818,7 +17820,7 @@
       <c r="W226" s="6"/>
       <c r="X226" s="7"/>
     </row>
-    <row r="227" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="227" spans="1:24" ht="33" customHeight="1">
       <c r="A227" s="6"/>
       <c r="B227" s="18"/>
       <c r="C227" s="6">
@@ -17876,7 +17878,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="228" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="228" spans="1:24" ht="33" customHeight="1">
       <c r="A228" s="6"/>
       <c r="B228" s="18"/>
       <c r="C228" s="6">
@@ -17934,7 +17936,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="229" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="229" spans="1:24" ht="33" customHeight="1">
       <c r="A229" s="6"/>
       <c r="B229" s="18"/>
       <c r="C229" s="6">
@@ -17988,7 +17990,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="230" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="230" spans="1:24" ht="33" customHeight="1">
       <c r="A230" s="6"/>
       <c r="B230" s="18"/>
       <c r="C230" s="6">
@@ -18038,7 +18040,7 @@
       <c r="W230" s="6"/>
       <c r="X230" s="7"/>
     </row>
-    <row r="231" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="231" spans="1:24" ht="33" customHeight="1">
       <c r="A231" s="6"/>
       <c r="B231" s="18"/>
       <c r="C231" s="6">
@@ -18086,7 +18088,7 @@
       </c>
       <c r="X231" s="7"/>
     </row>
-    <row r="232" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="232" spans="1:24" ht="33" customHeight="1">
       <c r="A232" s="6"/>
       <c r="B232" s="18"/>
       <c r="C232" s="6">
@@ -18142,7 +18144,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="233" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="233" spans="1:24" ht="33" customHeight="1">
       <c r="A233" s="6"/>
       <c r="B233" s="18"/>
       <c r="C233" s="6">
@@ -18192,7 +18194,7 @@
       <c r="W233" s="6"/>
       <c r="X233" s="7"/>
     </row>
-    <row r="234" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="234" spans="1:24" ht="33" customHeight="1">
       <c r="A234" s="6"/>
       <c r="B234" s="18"/>
       <c r="C234" s="6">
@@ -18240,7 +18242,7 @@
       </c>
       <c r="X234" s="7"/>
     </row>
-    <row r="235" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="235" spans="1:24" ht="33" customHeight="1">
       <c r="A235" s="6"/>
       <c r="B235" s="18"/>
       <c r="C235" s="6">
@@ -18296,7 +18298,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="236" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="236" spans="1:24" ht="33" customHeight="1">
       <c r="A236" s="6"/>
       <c r="B236" s="18"/>
       <c r="C236" s="6">
@@ -18346,7 +18348,7 @@
       <c r="W236" s="6"/>
       <c r="X236" s="7"/>
     </row>
-    <row r="237" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="237" spans="1:24" ht="33" customHeight="1">
       <c r="A237" s="6"/>
       <c r="B237" s="18"/>
       <c r="C237" s="6">
@@ -18394,7 +18396,7 @@
       </c>
       <c r="X237" s="7"/>
     </row>
-    <row r="238" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="238" spans="1:24" ht="33" customHeight="1">
       <c r="A238" s="6"/>
       <c r="B238" s="18"/>
       <c r="C238" s="6">
@@ -18450,7 +18452,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="239" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="239" spans="1:24" ht="33" customHeight="1">
       <c r="A239" s="6"/>
       <c r="B239" s="18"/>
       <c r="C239" s="6">
@@ -18500,7 +18502,7 @@
       <c r="W239" s="6"/>
       <c r="X239" s="7"/>
     </row>
-    <row r="240" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="240" spans="1:24" ht="33" customHeight="1">
       <c r="A240" s="6"/>
       <c r="B240" s="18"/>
       <c r="C240" s="6">
@@ -18548,7 +18550,7 @@
       </c>
       <c r="X240" s="7"/>
     </row>
-    <row r="241" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="241" spans="1:24" ht="33" customHeight="1">
       <c r="A241" s="6"/>
       <c r="B241" s="18"/>
       <c r="C241" s="6">
@@ -18604,7 +18606,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="242" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="242" spans="1:24" ht="33" customHeight="1">
       <c r="A242" s="6"/>
       <c r="B242" s="18"/>
       <c r="C242" s="6">
@@ -18654,7 +18656,7 @@
       <c r="W242" s="6"/>
       <c r="X242" s="7"/>
     </row>
-    <row r="243" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="243" spans="1:24" ht="33" customHeight="1">
       <c r="A243" s="6"/>
       <c r="B243" s="18"/>
       <c r="C243" s="6">
@@ -18702,7 +18704,7 @@
       </c>
       <c r="X243" s="7"/>
     </row>
-    <row r="244" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="244" spans="1:24" ht="33" customHeight="1">
       <c r="A244" s="6"/>
       <c r="B244" s="18"/>
       <c r="C244" s="6">
@@ -18758,7 +18760,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="245" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="245" spans="1:24" ht="33" customHeight="1">
       <c r="A245" s="6"/>
       <c r="B245" s="18"/>
       <c r="C245" s="6">
@@ -18808,7 +18810,7 @@
       <c r="W245" s="6"/>
       <c r="X245" s="7"/>
     </row>
-    <row r="246" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="246" spans="1:24" ht="33" customHeight="1">
       <c r="A246" s="6"/>
       <c r="B246" s="18"/>
       <c r="C246" s="6">
@@ -18856,7 +18858,7 @@
       </c>
       <c r="X246" s="7"/>
     </row>
-    <row r="247" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="247" spans="1:24" ht="33" customHeight="1">
       <c r="A247" s="6"/>
       <c r="B247" s="18"/>
       <c r="C247" s="6">
@@ -18912,7 +18914,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="248" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="248" spans="1:24" ht="33" customHeight="1">
       <c r="A248" s="6"/>
       <c r="B248" s="18"/>
       <c r="C248" s="6">
@@ -18962,7 +18964,7 @@
       <c r="W248" s="6"/>
       <c r="X248" s="7"/>
     </row>
-    <row r="249" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="249" spans="1:24" ht="33" customHeight="1">
       <c r="A249" s="6"/>
       <c r="B249" s="18"/>
       <c r="C249" s="6">
@@ -19010,7 +19012,7 @@
       </c>
       <c r="X249" s="7"/>
     </row>
-    <row r="250" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="250" spans="1:24" ht="33" customHeight="1">
       <c r="A250" s="6"/>
       <c r="B250" s="18"/>
       <c r="C250" s="6">
@@ -19060,7 +19062,7 @@
       <c r="W250" s="6"/>
       <c r="X250" s="7"/>
     </row>
-    <row r="251" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="251" spans="1:24" ht="33" customHeight="1">
       <c r="A251" s="6"/>
       <c r="B251" s="18"/>
       <c r="C251" s="6">
@@ -20876,7 +20878,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="283" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="283" spans="1:24" ht="33" customHeight="1">
       <c r="A283" s="6"/>
       <c r="B283" s="18"/>
       <c r="C283" s="6">
@@ -20930,7 +20932,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="284" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="284" spans="1:24" ht="33" customHeight="1">
       <c r="A284" s="6"/>
       <c r="B284" s="18"/>
       <c r="C284" s="6">
@@ -20984,7 +20986,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="285" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="285" spans="1:24" ht="33" customHeight="1">
       <c r="A285" s="6"/>
       <c r="B285" s="18"/>
       <c r="C285" s="6">
@@ -21038,7 +21040,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="286" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="286" spans="1:24" ht="33" customHeight="1">
       <c r="A286" s="6"/>
       <c r="B286" s="18"/>
       <c r="C286" s="6">
@@ -21092,7 +21094,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="287" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="287" spans="1:24" ht="33" customHeight="1">
       <c r="A287" s="6"/>
       <c r="B287" s="18"/>
       <c r="C287" s="6">
@@ -21146,7 +21148,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="288" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="288" spans="1:24" ht="33" customHeight="1">
       <c r="A288" s="6"/>
       <c r="B288" s="18"/>
       <c r="C288" s="6">
@@ -21200,7 +21202,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="289" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="289" spans="1:24" ht="33" customHeight="1">
       <c r="A289" s="6"/>
       <c r="B289" s="18"/>
       <c r="C289" s="6">
@@ -21254,7 +21256,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="290" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="290" spans="1:24" ht="33" customHeight="1">
       <c r="A290" s="6"/>
       <c r="B290" s="18"/>
       <c r="C290" s="6">
@@ -21308,7 +21310,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="291" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="291" spans="1:24" ht="33" customHeight="1">
       <c r="A291" s="6"/>
       <c r="B291" s="18"/>
       <c r="C291" s="6">
@@ -21362,7 +21364,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="292" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="292" spans="1:24" ht="33" customHeight="1">
       <c r="A292" s="6"/>
       <c r="B292" s="18"/>
       <c r="C292" s="6">
@@ -21416,7 +21418,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="293" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="293" spans="1:24" ht="33" customHeight="1">
       <c r="A293" s="6"/>
       <c r="B293" s="18"/>
       <c r="C293" s="6">
@@ -21470,7 +21472,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="294" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="294" spans="1:24" ht="33" customHeight="1">
       <c r="A294" s="6"/>
       <c r="B294" s="18"/>
       <c r="C294" s="6">
@@ -21526,7 +21528,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="295" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="295" spans="1:24" ht="33" customHeight="1">
       <c r="A295" s="6"/>
       <c r="B295" s="18"/>
       <c r="C295" s="6">
@@ -21580,7 +21582,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="296" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="296" spans="1:24" ht="33" customHeight="1">
       <c r="A296" s="6"/>
       <c r="B296" s="18"/>
       <c r="C296" s="6">
@@ -21634,7 +21636,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="297" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="297" spans="1:24" ht="33" customHeight="1">
       <c r="A297" s="6"/>
       <c r="B297" s="18"/>
       <c r="C297" s="6">
@@ -21688,7 +21690,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="298" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="298" spans="1:24" ht="33" customHeight="1">
       <c r="A298" s="6"/>
       <c r="B298" s="18"/>
       <c r="C298" s="6">
@@ -21742,7 +21744,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="299" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="299" spans="1:24" ht="33" customHeight="1">
       <c r="A299" s="6"/>
       <c r="B299" s="18"/>
       <c r="C299" s="6">
@@ -21796,7 +21798,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="300" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="300" spans="1:24" ht="33" customHeight="1">
       <c r="A300" s="6"/>
       <c r="B300" s="18"/>
       <c r="C300" s="6">
@@ -21850,7 +21852,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="301" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="301" spans="1:24" ht="33" customHeight="1">
       <c r="A301" s="6"/>
       <c r="B301" s="18"/>
       <c r="C301" s="6">
@@ -21904,7 +21906,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="302" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="302" spans="1:24" ht="33" customHeight="1">
       <c r="A302" s="6"/>
       <c r="B302" s="18"/>
       <c r="C302" s="6">
@@ -21958,7 +21960,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="303" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="303" spans="1:24" ht="33" customHeight="1">
       <c r="A303" s="6"/>
       <c r="B303" s="18"/>
       <c r="C303" s="6">
@@ -22012,7 +22014,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="304" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="304" spans="1:24" ht="33" customHeight="1">
       <c r="A304" s="6"/>
       <c r="B304" s="18"/>
       <c r="C304" s="6">
@@ -22066,7 +22068,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="33" hidden="1" customHeight="1">
+    <row r="305" spans="1:25" ht="33" customHeight="1">
       <c r="A305" s="6"/>
       <c r="B305" s="18"/>
       <c r="C305" s="6">
@@ -22120,7 +22122,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="33" hidden="1" customHeight="1">
+    <row r="306" spans="1:25" ht="33" customHeight="1">
       <c r="A306" s="6"/>
       <c r="B306" s="18"/>
       <c r="C306" s="6">
@@ -22174,7 +22176,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="33" hidden="1" customHeight="1">
+    <row r="307" spans="1:25" ht="33" customHeight="1">
       <c r="A307" s="6"/>
       <c r="B307" s="18"/>
       <c r="C307" s="6">
@@ -22344,7 +22346,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="60" hidden="1">
+    <row r="310" spans="1:25" ht="60">
       <c r="A310" s="6"/>
       <c r="B310" s="18"/>
       <c r="C310" s="6">
@@ -22401,7 +22403,7 @@
       </c>
       <c r="Y310"/>
     </row>
-    <row r="311" spans="1:25" ht="40" hidden="1">
+    <row r="311" spans="1:25" ht="40">
       <c r="A311" s="6"/>
       <c r="B311" s="18"/>
       <c r="C311" s="6">
@@ -22458,7 +22460,7 @@
       </c>
       <c r="Y311"/>
     </row>
-    <row r="312" spans="1:25" ht="40" hidden="1">
+    <row r="312" spans="1:25" ht="40">
       <c r="A312" s="6"/>
       <c r="B312" s="18"/>
       <c r="C312" s="6">
@@ -22515,7 +22517,7 @@
       </c>
       <c r="Y312"/>
     </row>
-    <row r="313" spans="1:25" ht="60" hidden="1">
+    <row r="313" spans="1:25" ht="60">
       <c r="A313" s="6"/>
       <c r="B313" s="18"/>
       <c r="C313" s="6">
@@ -22572,7 +22574,7 @@
       </c>
       <c r="Y313"/>
     </row>
-    <row r="314" spans="1:25" ht="40" hidden="1">
+    <row r="314" spans="1:25" ht="40">
       <c r="A314" s="6"/>
       <c r="B314" s="18"/>
       <c r="C314" s="6">
@@ -22629,7 +22631,7 @@
       </c>
       <c r="Y314"/>
     </row>
-    <row r="315" spans="1:25" ht="40" hidden="1">
+    <row r="315" spans="1:25" ht="40">
       <c r="A315" s="6"/>
       <c r="B315" s="18"/>
       <c r="C315" s="6">
@@ -22686,7 +22688,7 @@
       </c>
       <c r="Y315"/>
     </row>
-    <row r="316" spans="1:25" ht="40" hidden="1">
+    <row r="316" spans="1:25" ht="40">
       <c r="A316" s="6"/>
       <c r="B316" s="18"/>
       <c r="C316" s="6">
@@ -22743,7 +22745,7 @@
       </c>
       <c r="Y316"/>
     </row>
-    <row r="317" spans="1:25" ht="40" hidden="1">
+    <row r="317" spans="1:25" ht="40">
       <c r="A317" s="6"/>
       <c r="B317" s="18"/>
       <c r="C317" s="6">
@@ -22800,7 +22802,7 @@
       </c>
       <c r="Y317"/>
     </row>
-    <row r="318" spans="1:25" ht="40" hidden="1">
+    <row r="318" spans="1:25" ht="40">
       <c r="A318" s="6"/>
       <c r="B318" s="18"/>
       <c r="C318" s="6">
@@ -22857,7 +22859,7 @@
       </c>
       <c r="Y318"/>
     </row>
-    <row r="319" spans="1:25" ht="60" hidden="1">
+    <row r="319" spans="1:25" ht="60">
       <c r="A319" s="6"/>
       <c r="B319" s="18"/>
       <c r="C319" s="6">
@@ -22914,7 +22916,7 @@
       </c>
       <c r="Y319"/>
     </row>
-    <row r="320" spans="1:25" ht="40" hidden="1">
+    <row r="320" spans="1:25" ht="40">
       <c r="A320" s="6"/>
       <c r="B320" s="18"/>
       <c r="C320" s="6">
@@ -22971,7 +22973,7 @@
       </c>
       <c r="Y320"/>
     </row>
-    <row r="321" spans="1:26" ht="40" hidden="1">
+    <row r="321" spans="1:26" ht="40">
       <c r="A321" s="6"/>
       <c r="B321" s="18"/>
       <c r="C321" s="6">
@@ -23028,7 +23030,7 @@
       </c>
       <c r="Y321"/>
     </row>
-    <row r="322" spans="1:26" ht="40" hidden="1">
+    <row r="322" spans="1:26" ht="40">
       <c r="A322" s="6"/>
       <c r="B322" s="18"/>
       <c r="C322" s="6">
@@ -23085,7 +23087,7 @@
       </c>
       <c r="Y322"/>
     </row>
-    <row r="323" spans="1:26" ht="40" hidden="1">
+    <row r="323" spans="1:26" ht="40">
       <c r="A323" s="6"/>
       <c r="B323" s="18"/>
       <c r="C323" s="6">
@@ -23142,7 +23144,7 @@
       </c>
       <c r="Y323"/>
     </row>
-    <row r="324" spans="1:26" ht="40" hidden="1">
+    <row r="324" spans="1:26" ht="40">
       <c r="A324" s="6"/>
       <c r="B324" s="18"/>
       <c r="C324" s="6">
@@ -23199,7 +23201,7 @@
       </c>
       <c r="Y324"/>
     </row>
-    <row r="325" spans="1:26" ht="20" hidden="1">
+    <row r="325" spans="1:26" ht="20">
       <c r="A325" s="19" t="s">
         <v>1225</v>
       </c>
@@ -23231,7 +23233,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" spans="1:26" ht="20" hidden="1">
+    <row r="326" spans="1:26" ht="20">
       <c r="A326" s="19" t="s">
         <v>1223</v>
       </c>
@@ -23263,7 +23265,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" spans="1:26" ht="20" hidden="1">
+    <row r="327" spans="1:26" ht="20">
       <c r="A327" s="19" t="s">
         <v>1238</v>
       </c>
@@ -23295,7 +23297,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" spans="1:26" ht="20" hidden="1">
+    <row r="328" spans="1:26" ht="20">
       <c r="A328" s="19" t="s">
         <v>1224</v>
       </c>
@@ -23327,7 +23329,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" spans="1:26" ht="20" hidden="1">
+    <row r="329" spans="1:26" ht="20">
       <c r="A329" s="19" t="s">
         <v>1247</v>
       </c>
@@ -23359,7 +23361,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="1:26" ht="20" hidden="1">
+    <row r="330" spans="1:26" ht="20">
       <c r="A330" s="19" t="s">
         <v>1197</v>
       </c>
@@ -23391,7 +23393,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="1:26" ht="20" hidden="1">
+    <row r="331" spans="1:26" ht="20">
       <c r="A331" s="1" t="s">
         <v>1198</v>
       </c>
@@ -23401,42 +23403,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X331" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:X331" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="44">
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="X88:X89"/>
-    <mergeCell ref="X90:X91"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B84:B87"/>
     <mergeCell ref="X37:X39"/>
     <mergeCell ref="X34:X36"/>
     <mergeCell ref="A62:A63"/>
@@ -23453,6 +23421,34 @@
     <mergeCell ref="B80:B83"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="X88:X89"/>
+    <mergeCell ref="X90:X91"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A58"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.19685039370078741"/>

--- a/docs/mhlw/phase4_v08/001082795.xlsx
+++ b/docs/mhlw/phase4_v08/001082795.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0A31A6-070D-7545-8359-5F241CA6FE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B52E01B-C432-4AFF-80FB-C3A2EA5F0974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="付属2(健診項目一覧)" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'付属2(健診項目一覧)'!$A:$X</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'付属2(健診項目一覧)'!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -4356,7 +4358,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4597,22 +4599,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4704,9 +4706,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4744,7 +4746,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4850,7 +4852,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4992,7 +4994,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5000,35 +5002,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="9" style="5"/>
-    <col min="4" max="4" width="19.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="52.5" style="9" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="5" customWidth="1"/>
     <col min="9" max="10" width="7.5" style="5" customWidth="1"/>
     <col min="11" max="11" width="9.5" style="5" customWidth="1"/>
     <col min="12" max="14" width="8" style="5" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" style="14" customWidth="1"/>
+    <col min="15" max="15" width="16.875" style="14" customWidth="1"/>
     <col min="16" max="16" width="8" style="5" customWidth="1"/>
-    <col min="17" max="17" width="12.1640625" style="14" customWidth="1"/>
-    <col min="18" max="18" width="33.1640625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="12.125" style="14" customWidth="1"/>
+    <col min="18" max="18" width="33.125" style="9" customWidth="1"/>
     <col min="19" max="19" width="14.5" style="14" customWidth="1"/>
-    <col min="20" max="20" width="32.1640625" style="9" customWidth="1"/>
-    <col min="21" max="22" width="23.1640625" style="5" customWidth="1"/>
-    <col min="23" max="23" width="15.6640625" style="5" customWidth="1"/>
-    <col min="24" max="24" width="31.6640625" style="5" customWidth="1"/>
-    <col min="25" max="25" width="3.6640625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="32.125" style="9" customWidth="1"/>
+    <col min="21" max="22" width="23.125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="15.625" style="5" customWidth="1"/>
+    <col min="24" max="24" width="31.625" style="5" customWidth="1"/>
+    <col min="25" max="25" width="3.625" style="5" customWidth="1"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="63" customHeight="1">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>1215</v>
       </c>
@@ -5038,7 +5040,7 @@
       <c r="W1" s="10"/>
       <c r="X1" s="10"/>
     </row>
-    <row r="2" spans="1:24" ht="68">
+    <row r="2" spans="1:24" ht="60" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>1137</v>
       </c>
@@ -5112,7 +5114,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="33" customHeight="1">
+    <row r="3" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5170,7 +5172,7 @@
       <c r="W3" s="6"/>
       <c r="X3" s="7"/>
     </row>
-    <row r="4" spans="1:24" ht="33" customHeight="1">
+    <row r="4" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5228,7 +5230,7 @@
       <c r="W4" s="6"/>
       <c r="X4" s="7"/>
     </row>
-    <row r="5" spans="1:24" ht="33" customHeight="1">
+    <row r="5" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5286,11 +5288,11 @@
       <c r="W5" s="6"/>
       <c r="X5" s="7"/>
     </row>
-    <row r="6" spans="1:24" ht="33" customHeight="1">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C6" s="6">
@@ -5344,9 +5346,9 @@
       <c r="W6" s="6"/>
       <c r="X6" s="7"/>
     </row>
-    <row r="7" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
+    <row r="7" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="6">
         <v>10</v>
       </c>
@@ -5402,9 +5404,9 @@
       <c r="W7" s="6"/>
       <c r="X7" s="7"/>
     </row>
-    <row r="8" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
+    <row r="8" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="6">
         <v>10</v>
       </c>
@@ -5460,9 +5462,9 @@
       <c r="W8" s="6"/>
       <c r="X8" s="7"/>
     </row>
-    <row r="9" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
+    <row r="9" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="6">
         <v>10</v>
       </c>
@@ -5520,7 +5522,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="10" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="B10" s="18"/>
       <c r="C10" s="6">
@@ -5574,7 +5576,7 @@
       <c r="W10" s="6"/>
       <c r="X10" s="7"/>
     </row>
-    <row r="11" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="11" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="B11" s="18"/>
       <c r="C11" s="6">
@@ -5622,7 +5624,7 @@
       <c r="W11" s="6"/>
       <c r="X11" s="7"/>
     </row>
-    <row r="12" spans="1:24" ht="33" customHeight="1">
+    <row r="12" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5680,7 +5682,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="33" customHeight="1">
+    <row r="13" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5734,7 +5736,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="33" customHeight="1">
+    <row r="14" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5792,7 +5794,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="33" customHeight="1">
+    <row r="15" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5846,7 +5848,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="33" customHeight="1">
+    <row r="16" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5904,7 +5906,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="33" customHeight="1">
+    <row r="17" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>1131</v>
       </c>
@@ -5958,7 +5960,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="18" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6"/>
       <c r="B18" s="18"/>
       <c r="C18" s="6">
@@ -6006,7 +6008,7 @@
       <c r="W18" s="6"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="19" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="18"/>
       <c r="C19" s="6">
@@ -6054,7 +6056,7 @@
       <c r="W19" s="6"/>
       <c r="X19" s="7"/>
     </row>
-    <row r="20" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="20" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
       <c r="B20" s="18"/>
       <c r="C20" s="6">
@@ -6102,7 +6104,7 @@
       <c r="W20" s="6"/>
       <c r="X20" s="7"/>
     </row>
-    <row r="21" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="21" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
       <c r="B21" s="18"/>
       <c r="C21" s="6">
@@ -6150,7 +6152,7 @@
       <c r="W21" s="6"/>
       <c r="X21" s="7"/>
     </row>
-    <row r="22" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="22" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="B22" s="18"/>
       <c r="C22" s="6">
@@ -6204,11 +6206,11 @@
       <c r="W22" s="6"/>
       <c r="X22" s="7"/>
     </row>
-    <row r="23" spans="1:24" ht="33" customHeight="1">
-      <c r="A23" s="26" t="s">
+    <row r="23" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C23" s="6">
@@ -6268,9 +6270,9 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
+    <row r="24" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="6">
         <v>30</v>
       </c>
@@ -6326,9 +6328,9 @@
       <c r="W24" s="6"/>
       <c r="X24" s="7"/>
     </row>
-    <row r="25" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
+    <row r="25" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
       <c r="C25" s="6">
         <v>30</v>
       </c>
@@ -6384,11 +6386,11 @@
       <c r="W25" s="6"/>
       <c r="X25" s="7"/>
     </row>
-    <row r="26" spans="1:24" ht="33" customHeight="1">
-      <c r="A26" s="26" t="s">
+    <row r="26" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C26" s="6">
@@ -6448,9 +6450,9 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
+    <row r="27" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="6">
         <v>30</v>
       </c>
@@ -6506,9 +6508,9 @@
       <c r="W27" s="6"/>
       <c r="X27" s="7"/>
     </row>
-    <row r="28" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
+    <row r="28" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
       <c r="C28" s="6">
         <v>30</v>
       </c>
@@ -6564,7 +6566,7 @@
       <c r="W28" s="6"/>
       <c r="X28" s="7"/>
     </row>
-    <row r="29" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="29" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="B29" s="18"/>
       <c r="C29" s="6">
@@ -6618,7 +6620,7 @@
       <c r="W29" s="6"/>
       <c r="X29" s="7"/>
     </row>
-    <row r="30" spans="1:24" ht="60">
+    <row r="30" spans="1:24" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
         <v>1131</v>
       </c>
@@ -6676,8 +6678,8 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A31" s="26"/>
+    <row r="31" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="23"/>
       <c r="B31" s="18"/>
       <c r="C31" s="6">
         <v>50</v>
@@ -6734,8 +6736,8 @@
       <c r="W31" s="6"/>
       <c r="X31" s="7"/>
     </row>
-    <row r="32" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A32" s="28"/>
+    <row r="32" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="24"/>
       <c r="B32" s="18"/>
       <c r="C32" s="6">
         <v>50</v>
@@ -6792,8 +6794,8 @@
       <c r="W32" s="6"/>
       <c r="X32" s="7"/>
     </row>
-    <row r="33" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A33" s="27"/>
+    <row r="33" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="25"/>
       <c r="B33" s="18"/>
       <c r="C33" s="6">
         <v>50</v>
@@ -6850,11 +6852,11 @@
       <c r="W33" s="6"/>
       <c r="X33" s="7"/>
     </row>
-    <row r="34" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1">
-      <c r="A34" s="26" t="s">
+    <row r="34" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="23" t="s">
         <v>1132</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="23" t="s">
         <v>1132</v>
       </c>
       <c r="C34" s="6">
@@ -6912,13 +6914,13 @@
       <c r="W34" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X34" s="23" t="s">
+      <c r="X34" s="26" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="8" customFormat="1" ht="42" hidden="1" customHeight="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
+    <row r="35" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
       <c r="C35" s="6">
         <v>50</v>
       </c>
@@ -6974,11 +6976,11 @@
       <c r="W35" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X35" s="24"/>
-    </row>
-    <row r="36" spans="1:24" s="8" customFormat="1" ht="42" hidden="1" customHeight="1">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
+      <c r="X35" s="28"/>
+    </row>
+    <row r="36" spans="1:24" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
       <c r="C36" s="6">
         <v>50</v>
       </c>
@@ -7034,13 +7036,13 @@
       <c r="W36" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X36" s="25"/>
-    </row>
-    <row r="37" spans="1:24" ht="42" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:24" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="23" t="s">
         <v>1132</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="23" t="s">
         <v>1132</v>
       </c>
       <c r="C37" s="6">
@@ -7098,13 +7100,13 @@
       <c r="W37" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="X37" s="23" t="s">
+      <c r="X37" s="26" t="s">
         <v>1254</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="42" hidden="1" customHeight="1">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
+    <row r="38" spans="1:24" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="6">
         <v>50</v>
       </c>
@@ -7160,11 +7162,11 @@
       <c r="W38" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="X38" s="24"/>
-    </row>
-    <row r="39" spans="1:24" ht="42" hidden="1" customHeight="1">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
+      <c r="X38" s="28"/>
+    </row>
+    <row r="39" spans="1:24" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
       <c r="C39" s="6">
         <v>50</v>
       </c>
@@ -7220,13 +7222,13 @@
       <c r="W39" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="X39" s="25"/>
-    </row>
-    <row r="40" spans="1:24" ht="33" customHeight="1">
-      <c r="A40" s="26" t="s">
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C40" s="6">
@@ -7284,9 +7286,9 @@
       <c r="W40" s="6"/>
       <c r="X40" s="7"/>
     </row>
-    <row r="41" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
+    <row r="41" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="6">
         <v>50</v>
       </c>
@@ -7342,9 +7344,9 @@
       <c r="W41" s="6"/>
       <c r="X41" s="7"/>
     </row>
-    <row r="42" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
+    <row r="42" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
       <c r="C42" s="6">
         <v>50</v>
       </c>
@@ -7400,11 +7402,11 @@
       <c r="W42" s="6"/>
       <c r="X42" s="7"/>
     </row>
-    <row r="43" spans="1:24" ht="33" customHeight="1">
-      <c r="A43" s="26" t="s">
+    <row r="43" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C43" s="6">
@@ -7462,9 +7464,9 @@
       <c r="W43" s="6"/>
       <c r="X43" s="7"/>
     </row>
-    <row r="44" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
+    <row r="44" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="6">
         <v>50</v>
       </c>
@@ -7520,9 +7522,9 @@
       <c r="W44" s="6"/>
       <c r="X44" s="7"/>
     </row>
-    <row r="45" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
+    <row r="45" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
       <c r="C45" s="6">
         <v>50</v>
       </c>
@@ -7578,9 +7580,9 @@
       <c r="W45" s="6"/>
       <c r="X45" s="7"/>
     </row>
-    <row r="46" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
+    <row r="46" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
       <c r="C46" s="6">
         <v>50</v>
       </c>
@@ -7638,9 +7640,9 @@
       </c>
       <c r="X46" s="7"/>
     </row>
-    <row r="47" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
+    <row r="47" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="25"/>
+      <c r="B47" s="25"/>
       <c r="C47" s="6">
         <v>50</v>
       </c>
@@ -7696,8 +7698,8 @@
       </c>
       <c r="X47" s="7"/>
     </row>
-    <row r="48" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A48" s="26"/>
+    <row r="48" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="23"/>
       <c r="B48" s="18"/>
       <c r="C48" s="6">
         <v>50</v>
@@ -7754,8 +7756,8 @@
       <c r="W48" s="6"/>
       <c r="X48" s="7"/>
     </row>
-    <row r="49" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A49" s="27"/>
+    <row r="49" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="25"/>
       <c r="B49" s="18"/>
       <c r="C49" s="6">
         <v>50</v>
@@ -7812,11 +7814,11 @@
       <c r="W49" s="6"/>
       <c r="X49" s="7"/>
     </row>
-    <row r="50" spans="1:24" ht="33" customHeight="1">
-      <c r="A50" s="26" t="s">
+    <row r="50" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C50" s="6">
@@ -7874,9 +7876,9 @@
       <c r="W50" s="6"/>
       <c r="X50" s="7"/>
     </row>
-    <row r="51" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
+    <row r="51" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
       <c r="C51" s="6">
         <v>50</v>
       </c>
@@ -7932,11 +7934,11 @@
       <c r="W51" s="6"/>
       <c r="X51" s="7"/>
     </row>
-    <row r="52" spans="1:24" ht="33" customHeight="1">
-      <c r="A52" s="26" t="s">
+    <row r="52" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C52" s="6">
@@ -7994,9 +7996,9 @@
       <c r="W52" s="6"/>
       <c r="X52" s="7"/>
     </row>
-    <row r="53" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
+    <row r="53" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="25"/>
+      <c r="B53" s="25"/>
       <c r="C53" s="6">
         <v>50</v>
       </c>
@@ -8052,11 +8054,11 @@
       <c r="W53" s="6"/>
       <c r="X53" s="7"/>
     </row>
-    <row r="54" spans="1:24" ht="33" customHeight="1">
-      <c r="A54" s="26" t="s">
+    <row r="54" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C54" s="6">
@@ -8114,9 +8116,9 @@
       <c r="W54" s="6"/>
       <c r="X54" s="7"/>
     </row>
-    <row r="55" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
+    <row r="55" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="25"/>
+      <c r="B55" s="25"/>
       <c r="C55" s="6">
         <v>50</v>
       </c>
@@ -8172,8 +8174,8 @@
       <c r="W55" s="6"/>
       <c r="X55" s="7"/>
     </row>
-    <row r="56" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A56" s="26"/>
+    <row r="56" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="23"/>
       <c r="B56" s="18"/>
       <c r="C56" s="6">
         <v>50</v>
@@ -8230,8 +8232,8 @@
       <c r="W56" s="6"/>
       <c r="X56" s="7"/>
     </row>
-    <row r="57" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A57" s="28"/>
+    <row r="57" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="24"/>
       <c r="B57" s="18"/>
       <c r="C57" s="6">
         <v>50</v>
@@ -8290,8 +8292,8 @@
       </c>
       <c r="X57" s="7"/>
     </row>
-    <row r="58" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A58" s="27"/>
+    <row r="58" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="25"/>
       <c r="B58" s="18"/>
       <c r="C58" s="6">
         <v>50</v>
@@ -8348,8 +8350,8 @@
       <c r="W58" s="6"/>
       <c r="X58" s="7"/>
     </row>
-    <row r="59" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A59" s="26"/>
+    <row r="59" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="23"/>
       <c r="B59" s="18"/>
       <c r="C59" s="6">
         <v>50</v>
@@ -8408,8 +8410,8 @@
       </c>
       <c r="X59" s="7"/>
     </row>
-    <row r="60" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A60" s="28"/>
+    <row r="60" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="24"/>
       <c r="B60" s="18"/>
       <c r="C60" s="6">
         <v>50</v>
@@ -8468,8 +8470,8 @@
       </c>
       <c r="X60" s="7"/>
     </row>
-    <row r="61" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A61" s="27"/>
+    <row r="61" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="25"/>
       <c r="B61" s="18"/>
       <c r="C61" s="6">
         <v>50</v>
@@ -8528,11 +8530,11 @@
       </c>
       <c r="X61" s="7"/>
     </row>
-    <row r="62" spans="1:24" ht="33" customHeight="1">
-      <c r="A62" s="26" t="s">
+    <row r="62" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="23" t="s">
         <v>1141</v>
       </c>
-      <c r="B62" s="26" t="s">
+      <c r="B62" s="23" t="s">
         <v>1279</v>
       </c>
       <c r="C62" s="6">
@@ -8594,9 +8596,9 @@
       <c r="W62" s="6"/>
       <c r="X62" s="7"/>
     </row>
-    <row r="63" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A63" s="27"/>
-      <c r="B63" s="27"/>
+    <row r="63" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
       <c r="C63" s="6">
         <v>50</v>
       </c>
@@ -8656,7 +8658,7 @@
       <c r="W63" s="6"/>
       <c r="X63" s="7"/>
     </row>
-    <row r="64" spans="1:24" ht="33" customHeight="1">
+    <row r="64" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>1141</v>
       </c>
@@ -8718,7 +8720,7 @@
       </c>
       <c r="X64" s="7"/>
     </row>
-    <row r="65" spans="1:24" ht="100">
+    <row r="65" spans="1:24" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A65" s="6" t="s">
         <v>1141</v>
       </c>
@@ -8778,7 +8780,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="33" customHeight="1">
+    <row r="66" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6" t="s">
         <v>1141</v>
       </c>
@@ -8846,7 +8848,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="67" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="6"/>
       <c r="B67" s="18"/>
       <c r="C67" s="6">
@@ -8904,7 +8906,7 @@
       <c r="W67" s="6"/>
       <c r="X67" s="7"/>
     </row>
-    <row r="68" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="68" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6"/>
       <c r="B68" s="18"/>
       <c r="C68" s="6">
@@ -8962,7 +8964,7 @@
       <c r="W68" s="6"/>
       <c r="X68" s="7"/>
     </row>
-    <row r="69" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="69" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6"/>
       <c r="B69" s="18"/>
       <c r="C69" s="6">
@@ -9020,7 +9022,7 @@
       <c r="W69" s="6"/>
       <c r="X69" s="7"/>
     </row>
-    <row r="70" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="70" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="6"/>
       <c r="B70" s="18"/>
       <c r="C70" s="6">
@@ -9078,7 +9080,7 @@
       <c r="W70" s="6"/>
       <c r="X70" s="7"/>
     </row>
-    <row r="71" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="71" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="6"/>
       <c r="B71" s="18"/>
       <c r="C71" s="6">
@@ -9136,7 +9138,7 @@
       <c r="W71" s="6"/>
       <c r="X71" s="7"/>
     </row>
-    <row r="72" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="72" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6"/>
       <c r="B72" s="18"/>
       <c r="C72" s="6">
@@ -9194,7 +9196,7 @@
       <c r="W72" s="6"/>
       <c r="X72" s="7"/>
     </row>
-    <row r="73" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="73" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6"/>
       <c r="B73" s="18"/>
       <c r="C73" s="6">
@@ -9246,7 +9248,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="74" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="6"/>
       <c r="B74" s="18"/>
       <c r="C74" s="6">
@@ -9304,7 +9306,7 @@
       <c r="W74" s="6"/>
       <c r="X74" s="7"/>
     </row>
-    <row r="75" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="75" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="6"/>
       <c r="B75" s="18"/>
       <c r="C75" s="6">
@@ -9362,11 +9364,11 @@
       <c r="W75" s="6"/>
       <c r="X75" s="7"/>
     </row>
-    <row r="76" spans="1:24" ht="33" customHeight="1">
-      <c r="A76" s="26" t="s">
+    <row r="76" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="23" t="s">
         <v>1280</v>
       </c>
-      <c r="B76" s="26" t="s">
+      <c r="B76" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C76" s="6">
@@ -9422,13 +9424,13 @@
         <v>26</v>
       </c>
       <c r="W76" s="6"/>
-      <c r="X76" s="23" t="s">
+      <c r="X76" s="26" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A77" s="28"/>
-      <c r="B77" s="28"/>
+    <row r="77" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="24"/>
+      <c r="B77" s="24"/>
       <c r="C77" s="6">
         <v>60</v>
       </c>
@@ -9482,11 +9484,11 @@
         <v>26</v>
       </c>
       <c r="W77" s="6"/>
-      <c r="X77" s="24"/>
-    </row>
-    <row r="78" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A78" s="28"/>
-      <c r="B78" s="28"/>
+      <c r="X77" s="28"/>
+    </row>
+    <row r="78" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="24"/>
+      <c r="B78" s="24"/>
       <c r="C78" s="6">
         <v>60</v>
       </c>
@@ -9540,11 +9542,11 @@
         <v>26</v>
       </c>
       <c r="W78" s="6"/>
-      <c r="X78" s="24"/>
-    </row>
-    <row r="79" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A79" s="27"/>
-      <c r="B79" s="27"/>
+      <c r="X78" s="28"/>
+    </row>
+    <row r="79" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="25"/>
+      <c r="B79" s="25"/>
       <c r="C79" s="6">
         <v>60</v>
       </c>
@@ -9598,13 +9600,13 @@
         <v>26</v>
       </c>
       <c r="W79" s="6"/>
-      <c r="X79" s="25"/>
-    </row>
-    <row r="80" spans="1:24" ht="33" customHeight="1">
-      <c r="A80" s="26" t="s">
+      <c r="X79" s="27"/>
+    </row>
+    <row r="80" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="23" t="s">
         <v>1280</v>
       </c>
-      <c r="B80" s="26" t="s">
+      <c r="B80" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C80" s="6">
@@ -9660,13 +9662,13 @@
         <v>26</v>
       </c>
       <c r="W80" s="6"/>
-      <c r="X80" s="23" t="s">
+      <c r="X80" s="26" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A81" s="28"/>
-      <c r="B81" s="28"/>
+    <row r="81" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="24"/>
+      <c r="B81" s="24"/>
       <c r="C81" s="6">
         <v>60</v>
       </c>
@@ -9720,11 +9722,11 @@
         <v>26</v>
       </c>
       <c r="W81" s="6"/>
-      <c r="X81" s="24"/>
-    </row>
-    <row r="82" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A82" s="28"/>
-      <c r="B82" s="28"/>
+      <c r="X81" s="28"/>
+    </row>
+    <row r="82" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="24"/>
+      <c r="B82" s="24"/>
       <c r="C82" s="6">
         <v>60</v>
       </c>
@@ -9778,11 +9780,11 @@
         <v>26</v>
       </c>
       <c r="W82" s="6"/>
-      <c r="X82" s="24"/>
-    </row>
-    <row r="83" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A83" s="27"/>
-      <c r="B83" s="27"/>
+      <c r="X82" s="28"/>
+    </row>
+    <row r="83" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
       <c r="C83" s="6">
         <v>60</v>
       </c>
@@ -9836,13 +9838,13 @@
         <v>26</v>
       </c>
       <c r="W83" s="6"/>
-      <c r="X83" s="25"/>
-    </row>
-    <row r="84" spans="1:24" ht="33" customHeight="1">
-      <c r="A84" s="26" t="s">
+      <c r="X83" s="27"/>
+    </row>
+    <row r="84" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="23" t="s">
         <v>1280</v>
       </c>
-      <c r="B84" s="26" t="s">
+      <c r="B84" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C84" s="6">
@@ -9902,9 +9904,9 @@
       </c>
       <c r="X84" s="7"/>
     </row>
-    <row r="85" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A85" s="28"/>
-      <c r="B85" s="28"/>
+    <row r="85" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
       <c r="C85" s="6">
         <v>60</v>
       </c>
@@ -9962,9 +9964,9 @@
       </c>
       <c r="X85" s="7"/>
     </row>
-    <row r="86" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A86" s="28"/>
-      <c r="B86" s="28"/>
+    <row r="86" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="24"/>
+      <c r="B86" s="24"/>
       <c r="C86" s="6">
         <v>60</v>
       </c>
@@ -10022,9 +10024,9 @@
       </c>
       <c r="X86" s="7"/>
     </row>
-    <row r="87" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A87" s="27"/>
-      <c r="B87" s="27"/>
+    <row r="87" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
       <c r="C87" s="6">
         <v>60</v>
       </c>
@@ -10082,11 +10084,11 @@
       </c>
       <c r="X87" s="7"/>
     </row>
-    <row r="88" spans="1:24" ht="33" customHeight="1">
-      <c r="A88" s="26" t="s">
+    <row r="88" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B88" s="26" t="s">
+      <c r="B88" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C88" s="6">
@@ -10140,13 +10142,13 @@
         <v>26</v>
       </c>
       <c r="W88" s="6"/>
-      <c r="X88" s="23" t="s">
+      <c r="X88" s="26" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A89" s="27"/>
-      <c r="B89" s="27"/>
+    <row r="89" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="25"/>
+      <c r="B89" s="25"/>
       <c r="C89" s="6">
         <v>70</v>
       </c>
@@ -10198,13 +10200,13 @@
         <v>26</v>
       </c>
       <c r="W89" s="6"/>
-      <c r="X89" s="25"/>
-    </row>
-    <row r="90" spans="1:24" ht="33" customHeight="1">
-      <c r="A90" s="26" t="s">
+      <c r="X89" s="27"/>
+    </row>
+    <row r="90" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="23" t="s">
         <v>1131</v>
       </c>
-      <c r="B90" s="26" t="s">
+      <c r="B90" s="23" t="s">
         <v>1131</v>
       </c>
       <c r="C90" s="6">
@@ -10258,13 +10260,13 @@
         <v>26</v>
       </c>
       <c r="W90" s="6"/>
-      <c r="X90" s="23" t="s">
+      <c r="X90" s="26" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A91" s="27"/>
-      <c r="B91" s="27"/>
+    <row r="91" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="25"/>
+      <c r="B91" s="25"/>
       <c r="C91" s="6">
         <v>70</v>
       </c>
@@ -10316,10 +10318,10 @@
         <v>26</v>
       </c>
       <c r="W91" s="6"/>
-      <c r="X91" s="25"/>
-    </row>
-    <row r="92" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A92" s="26"/>
+      <c r="X91" s="27"/>
+    </row>
+    <row r="92" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="23"/>
       <c r="B92" s="18"/>
       <c r="C92" s="6">
         <v>70</v>
@@ -10372,12 +10374,12 @@
         <v>26</v>
       </c>
       <c r="W92" s="6"/>
-      <c r="X92" s="23" t="s">
+      <c r="X92" s="26" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="33" hidden="1" customHeight="1">
-      <c r="A93" s="27"/>
+    <row r="93" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="25"/>
       <c r="B93" s="18"/>
       <c r="C93" s="6">
         <v>70</v>
@@ -10430,9 +10432,9 @@
         <v>26</v>
       </c>
       <c r="W93" s="6"/>
-      <c r="X93" s="25"/>
-    </row>
-    <row r="94" spans="1:24" ht="33" hidden="1" customHeight="1">
+      <c r="X93" s="27"/>
+    </row>
+    <row r="94" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="6"/>
       <c r="B94" s="18"/>
       <c r="C94" s="6">
@@ -10486,7 +10488,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="95" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="6"/>
       <c r="B95" s="18"/>
       <c r="C95" s="6">
@@ -10536,7 +10538,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="96" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="6"/>
       <c r="B96" s="18"/>
       <c r="C96" s="6">
@@ -10590,7 +10592,7 @@
       <c r="W96" s="6"/>
       <c r="X96" s="7"/>
     </row>
-    <row r="97" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="97" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="6"/>
       <c r="B97" s="18"/>
       <c r="C97" s="6">
@@ -10644,7 +10646,7 @@
       <c r="W97" s="6"/>
       <c r="X97" s="7"/>
     </row>
-    <row r="98" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="98" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="6"/>
       <c r="B98" s="18"/>
       <c r="C98" s="6">
@@ -10704,7 +10706,7 @@
       </c>
       <c r="X98" s="7"/>
     </row>
-    <row r="99" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="99" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="6"/>
       <c r="B99" s="18"/>
       <c r="C99" s="6">
@@ -10764,7 +10766,7 @@
       </c>
       <c r="X99" s="7"/>
     </row>
-    <row r="100" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="100" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="6"/>
       <c r="B100" s="18"/>
       <c r="C100" s="6">
@@ -10824,7 +10826,7 @@
       </c>
       <c r="X100" s="7"/>
     </row>
-    <row r="101" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="101" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6"/>
       <c r="B101" s="18"/>
       <c r="C101" s="6">
@@ -10884,7 +10886,7 @@
       </c>
       <c r="X101" s="7"/>
     </row>
-    <row r="102" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="102" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="6"/>
       <c r="B102" s="18"/>
       <c r="C102" s="6">
@@ -10944,7 +10946,7 @@
       </c>
       <c r="X102" s="7"/>
     </row>
-    <row r="103" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="103" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="6"/>
       <c r="B103" s="18"/>
       <c r="C103" s="6">
@@ -11004,7 +11006,7 @@
       </c>
       <c r="X103" s="7"/>
     </row>
-    <row r="104" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="104" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="6"/>
       <c r="B104" s="18"/>
       <c r="C104" s="6">
@@ -11064,7 +11066,7 @@
       </c>
       <c r="X104" s="7"/>
     </row>
-    <row r="105" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="105" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="6"/>
       <c r="B105" s="18"/>
       <c r="C105" s="6">
@@ -11124,7 +11126,7 @@
       </c>
       <c r="X105" s="7"/>
     </row>
-    <row r="106" spans="1:24" ht="33" customHeight="1">
+    <row r="106" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11188,7 +11190,7 @@
       <c r="W106" s="6"/>
       <c r="X106" s="7"/>
     </row>
-    <row r="107" spans="1:24" ht="33" customHeight="1">
+    <row r="107" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11252,7 +11254,7 @@
       <c r="W107" s="6"/>
       <c r="X107" s="7"/>
     </row>
-    <row r="108" spans="1:24" ht="33" customHeight="1">
+    <row r="108" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11316,7 +11318,7 @@
       <c r="W108" s="6"/>
       <c r="X108" s="7"/>
     </row>
-    <row r="109" spans="1:24" ht="33" customHeight="1">
+    <row r="109" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11374,7 +11376,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="110" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="110" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="6"/>
       <c r="B110" s="18"/>
       <c r="C110" s="6">
@@ -11434,7 +11436,7 @@
       <c r="W110" s="6"/>
       <c r="X110" s="7"/>
     </row>
-    <row r="111" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="111" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="6"/>
       <c r="B111" s="18"/>
       <c r="C111" s="6">
@@ -11494,7 +11496,7 @@
       <c r="W111" s="6"/>
       <c r="X111" s="7"/>
     </row>
-    <row r="112" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="112" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="6"/>
       <c r="B112" s="18"/>
       <c r="C112" s="6">
@@ -11554,7 +11556,7 @@
       <c r="W112" s="6"/>
       <c r="X112" s="7"/>
     </row>
-    <row r="113" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="113" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="6"/>
       <c r="B113" s="18"/>
       <c r="C113" s="6">
@@ -11614,7 +11616,7 @@
       <c r="W113" s="6"/>
       <c r="X113" s="7"/>
     </row>
-    <row r="114" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="114" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="6"/>
       <c r="B114" s="18"/>
       <c r="C114" s="6">
@@ -11674,7 +11676,7 @@
       <c r="W114" s="6"/>
       <c r="X114" s="7"/>
     </row>
-    <row r="115" spans="1:24" ht="33" customHeight="1">
+    <row r="115" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11736,7 +11738,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="116" spans="1:24" ht="33" customHeight="1">
+    <row r="116" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11794,7 +11796,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="80">
+    <row r="117" spans="1:24" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A117" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11858,7 +11860,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="33" customHeight="1">
+    <row r="118" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="6" t="s">
         <v>1141</v>
       </c>
@@ -11916,7 +11918,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="119" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="119" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="6"/>
       <c r="B119" s="18"/>
       <c r="C119" s="6">
@@ -11978,7 +11980,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="120" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="6"/>
       <c r="B120" s="18"/>
       <c r="C120" s="6">
@@ -12040,7 +12042,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="121" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="121" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="6"/>
       <c r="B121" s="18"/>
       <c r="C121" s="6">
@@ -12098,7 +12100,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="122" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="122" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="6"/>
       <c r="B122" s="18"/>
       <c r="C122" s="6">
@@ -12156,7 +12158,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="123" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="6"/>
       <c r="B123" s="18"/>
       <c r="C123" s="6">
@@ -12212,7 +12214,7 @@
       <c r="W123" s="6"/>
       <c r="X123" s="7"/>
     </row>
-    <row r="124" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="124" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="6"/>
       <c r="B124" s="18"/>
       <c r="C124" s="6">
@@ -12274,7 +12276,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="125" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="125" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="6"/>
       <c r="B125" s="18"/>
       <c r="C125" s="6">
@@ -12336,7 +12338,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="126" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="126" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="6"/>
       <c r="B126" s="18"/>
       <c r="C126" s="6">
@@ -12394,7 +12396,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="127" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="6"/>
       <c r="B127" s="18"/>
       <c r="C127" s="6">
@@ -12452,7 +12454,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="128" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="6"/>
       <c r="B128" s="18"/>
       <c r="C128" s="6">
@@ -12508,7 +12510,7 @@
       <c r="W128" s="6"/>
       <c r="X128" s="7"/>
     </row>
-    <row r="129" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="129" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="6"/>
       <c r="B129" s="18"/>
       <c r="C129" s="6">
@@ -12562,7 +12564,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="130" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="6"/>
       <c r="B130" s="18"/>
       <c r="C130" s="6">
@@ -12612,7 +12614,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="131" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="6"/>
       <c r="B131" s="18"/>
       <c r="C131" s="6">
@@ -12666,7 +12668,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="132" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="6"/>
       <c r="B132" s="18"/>
       <c r="C132" s="6">
@@ -12720,7 +12722,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="133" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="6"/>
       <c r="B133" s="18"/>
       <c r="C133" s="6">
@@ -12774,7 +12776,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="134" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="6"/>
       <c r="B134" s="18"/>
       <c r="C134" s="6">
@@ -12832,7 +12834,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="135" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="6"/>
       <c r="B135" s="18"/>
       <c r="C135" s="6">
@@ -12890,7 +12892,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="136" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="6"/>
       <c r="B136" s="18"/>
       <c r="C136" s="6">
@@ -12944,7 +12946,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="137" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="6"/>
       <c r="B137" s="18"/>
       <c r="C137" s="6">
@@ -12998,7 +13000,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="138" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="138" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="6"/>
       <c r="B138" s="18"/>
       <c r="C138" s="6">
@@ -13050,7 +13052,7 @@
       <c r="W138" s="6"/>
       <c r="X138" s="7"/>
     </row>
-    <row r="139" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="139" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="6"/>
       <c r="B139" s="18"/>
       <c r="C139" s="6">
@@ -13108,7 +13110,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="140" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="140" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="6"/>
       <c r="B140" s="18"/>
       <c r="C140" s="6">
@@ -13162,7 +13164,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="141" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="6"/>
       <c r="B141" s="18"/>
       <c r="C141" s="6">
@@ -13216,7 +13218,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="142" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="142" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="6"/>
       <c r="B142" s="18"/>
       <c r="C142" s="6">
@@ -13268,7 +13270,7 @@
       <c r="W142" s="6"/>
       <c r="X142" s="7"/>
     </row>
-    <row r="143" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="143" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="6"/>
       <c r="B143" s="18"/>
       <c r="C143" s="6">
@@ -13326,7 +13328,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="144" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="144" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="6"/>
       <c r="B144" s="18"/>
       <c r="C144" s="6">
@@ -13380,7 +13382,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="145" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="145" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="6"/>
       <c r="B145" s="18"/>
       <c r="C145" s="6">
@@ -13434,7 +13436,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="146" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="146" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="6"/>
       <c r="B146" s="18"/>
       <c r="C146" s="6">
@@ -13486,7 +13488,7 @@
       <c r="W146" s="6"/>
       <c r="X146" s="7"/>
     </row>
-    <row r="147" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="147" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="6"/>
       <c r="B147" s="18"/>
       <c r="C147" s="6">
@@ -13540,7 +13542,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="148" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="148" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="6"/>
       <c r="B148" s="18"/>
       <c r="C148" s="6">
@@ -13590,7 +13592,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="149" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="6"/>
       <c r="B149" s="18"/>
       <c r="C149" s="6">
@@ -13646,7 +13648,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="150" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="150" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="6"/>
       <c r="B150" s="18"/>
       <c r="C150" s="6">
@@ -13700,7 +13702,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="151" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="151" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="6"/>
       <c r="B151" s="18"/>
       <c r="C151" s="6">
@@ -13750,7 +13752,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="152" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="6"/>
       <c r="B152" s="18"/>
       <c r="C152" s="6">
@@ -13804,7 +13806,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="153" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="6"/>
       <c r="B153" s="18"/>
       <c r="C153" s="6">
@@ -13854,7 +13856,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="154" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="154" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="6"/>
       <c r="B154" s="18"/>
       <c r="C154" s="6">
@@ -13908,7 +13910,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="155" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="6"/>
       <c r="B155" s="18"/>
       <c r="C155" s="6">
@@ -13958,7 +13960,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="156" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="156" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="6"/>
       <c r="B156" s="18"/>
       <c r="C156" s="6">
@@ -14012,7 +14014,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="157" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="6"/>
       <c r="B157" s="18"/>
       <c r="C157" s="6">
@@ -14062,7 +14064,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="158" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="158" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="6"/>
       <c r="B158" s="18"/>
       <c r="C158" s="6">
@@ -14116,7 +14118,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="159" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="159" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="6"/>
       <c r="B159" s="18"/>
       <c r="C159" s="6">
@@ -14166,7 +14168,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="160" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="160" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="6"/>
       <c r="B160" s="18"/>
       <c r="C160" s="6">
@@ -14220,7 +14222,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="161" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="6"/>
       <c r="B161" s="18"/>
       <c r="C161" s="6">
@@ -14270,7 +14272,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="162" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="6"/>
       <c r="B162" s="18"/>
       <c r="C162" s="6">
@@ -14324,7 +14326,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="163" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="6"/>
       <c r="B163" s="18"/>
       <c r="C163" s="6">
@@ -14374,7 +14376,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="164" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="164" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="6"/>
       <c r="B164" s="18"/>
       <c r="C164" s="6">
@@ -14428,7 +14430,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="165" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="165" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="6"/>
       <c r="B165" s="18"/>
       <c r="C165" s="6">
@@ -14484,7 +14486,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="166" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="166" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="6"/>
       <c r="B166" s="18"/>
       <c r="C166" s="6">
@@ -14538,7 +14540,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="167" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="167" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="6"/>
       <c r="B167" s="18"/>
       <c r="C167" s="6">
@@ -14592,7 +14594,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="168" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="168" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="6"/>
       <c r="B168" s="18"/>
       <c r="C168" s="6">
@@ -14642,7 +14644,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="169" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="169" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="6"/>
       <c r="B169" s="18"/>
       <c r="C169" s="6">
@@ -14696,7 +14698,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="170" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="170" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="6"/>
       <c r="B170" s="18"/>
       <c r="C170" s="6">
@@ -14746,7 +14748,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="171" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="171" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="6"/>
       <c r="B171" s="18"/>
       <c r="C171" s="6">
@@ -14802,7 +14804,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="172" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="172" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="6"/>
       <c r="B172" s="18"/>
       <c r="C172" s="6">
@@ -14858,7 +14860,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="173" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="173" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="6"/>
       <c r="B173" s="18"/>
       <c r="C173" s="6">
@@ -14912,7 +14914,7 @@
       <c r="W173" s="6"/>
       <c r="X173" s="7"/>
     </row>
-    <row r="174" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="174" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="6"/>
       <c r="B174" s="18"/>
       <c r="C174" s="6">
@@ -14966,7 +14968,7 @@
       <c r="W174" s="6"/>
       <c r="X174" s="7"/>
     </row>
-    <row r="175" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="175" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="6"/>
       <c r="B175" s="18"/>
       <c r="C175" s="6">
@@ -15020,7 +15022,7 @@
       <c r="W175" s="6"/>
       <c r="X175" s="7"/>
     </row>
-    <row r="176" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="176" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="6"/>
       <c r="B176" s="18"/>
       <c r="C176" s="6">
@@ -15074,7 +15076,7 @@
       <c r="W176" s="6"/>
       <c r="X176" s="7"/>
     </row>
-    <row r="177" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="177" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="6"/>
       <c r="B177" s="18"/>
       <c r="C177" s="6">
@@ -15124,7 +15126,7 @@
       <c r="W177" s="6"/>
       <c r="X177" s="7"/>
     </row>
-    <row r="178" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="178" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="6"/>
       <c r="B178" s="18"/>
       <c r="C178" s="6">
@@ -15174,7 +15176,7 @@
       <c r="W178" s="6"/>
       <c r="X178" s="7"/>
     </row>
-    <row r="179" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="179" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="6"/>
       <c r="B179" s="18"/>
       <c r="C179" s="6">
@@ -15224,7 +15226,7 @@
       <c r="W179" s="6"/>
       <c r="X179" s="7"/>
     </row>
-    <row r="180" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="180" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="6"/>
       <c r="B180" s="18"/>
       <c r="C180" s="6">
@@ -15274,7 +15276,7 @@
       <c r="W180" s="6"/>
       <c r="X180" s="7"/>
     </row>
-    <row r="181" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="181" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="6"/>
       <c r="B181" s="18"/>
       <c r="C181" s="6">
@@ -15328,7 +15330,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="182" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="182" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="6"/>
       <c r="B182" s="18"/>
       <c r="C182" s="6">
@@ -15382,7 +15384,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="183" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="183" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="6"/>
       <c r="B183" s="18"/>
       <c r="C183" s="6">
@@ -15436,7 +15438,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="184" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="184" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="6"/>
       <c r="B184" s="18"/>
       <c r="C184" s="6">
@@ -15490,7 +15492,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="185" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="185" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="6"/>
       <c r="B185" s="18"/>
       <c r="C185" s="6">
@@ -15544,7 +15546,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="186" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="186" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="6"/>
       <c r="B186" s="18"/>
       <c r="C186" s="6">
@@ -15592,7 +15594,7 @@
       <c r="W186" s="6"/>
       <c r="X186" s="7"/>
     </row>
-    <row r="187" spans="1:24" ht="33" customHeight="1">
+    <row r="187" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="6" t="s">
         <v>1141</v>
       </c>
@@ -15654,7 +15656,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="188" spans="1:24" ht="33" customHeight="1">
+    <row r="188" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="6" t="s">
         <v>1141</v>
       </c>
@@ -15716,7 +15718,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="189" spans="1:24" ht="33" customHeight="1">
+    <row r="189" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="6" t="s">
         <v>1141</v>
       </c>
@@ -15778,7 +15780,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="190" spans="1:24" ht="55.5" customHeight="1">
+    <row r="190" spans="1:24" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="6" t="s">
         <v>1141</v>
       </c>
@@ -15840,7 +15842,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="191" spans="1:24" ht="33" customHeight="1">
+    <row r="191" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="6" t="s">
         <v>1141</v>
       </c>
@@ -15904,7 +15906,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="192" spans="1:24" ht="33" customHeight="1">
+    <row r="192" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="6" t="s">
         <v>1141</v>
       </c>
@@ -15968,7 +15970,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="193" spans="1:24" ht="33" customHeight="1">
+    <row r="193" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="6" t="s">
         <v>1141</v>
       </c>
@@ -16026,7 +16028,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="194" spans="1:24" ht="33" customHeight="1">
+    <row r="194" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="6" t="s">
         <v>1141</v>
       </c>
@@ -16090,7 +16092,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="195" spans="1:24" ht="33" customHeight="1">
+    <row r="195" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="6" t="s">
         <v>1141</v>
       </c>
@@ -16148,7 +16150,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="196" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="196" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="6"/>
       <c r="B196" s="18"/>
       <c r="C196" s="6">
@@ -16202,7 +16204,7 @@
       <c r="W196" s="6"/>
       <c r="X196" s="7"/>
     </row>
-    <row r="197" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="197" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="6"/>
       <c r="B197" s="18"/>
       <c r="C197" s="6">
@@ -16256,7 +16258,7 @@
       <c r="W197" s="6"/>
       <c r="X197" s="7"/>
     </row>
-    <row r="198" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="198" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="6"/>
       <c r="B198" s="18"/>
       <c r="C198" s="6">
@@ -16314,7 +16316,7 @@
       <c r="W198" s="6"/>
       <c r="X198" s="7"/>
     </row>
-    <row r="199" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="199" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="6"/>
       <c r="B199" s="18"/>
       <c r="C199" s="6">
@@ -16372,7 +16374,7 @@
       <c r="W199" s="6"/>
       <c r="X199" s="7"/>
     </row>
-    <row r="200" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="200" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="6"/>
       <c r="B200" s="18"/>
       <c r="C200" s="6">
@@ -16430,7 +16432,7 @@
       <c r="W200" s="6"/>
       <c r="X200" s="7"/>
     </row>
-    <row r="201" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="201" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="6"/>
       <c r="B201" s="18"/>
       <c r="C201" s="6">
@@ -16488,7 +16490,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="202" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="202" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="6"/>
       <c r="B202" s="18"/>
       <c r="C202" s="6">
@@ -16546,7 +16548,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="203" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="203" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="6"/>
       <c r="B203" s="18"/>
       <c r="C203" s="6">
@@ -16604,7 +16606,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="204" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="204" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="6"/>
       <c r="B204" s="18"/>
       <c r="C204" s="6">
@@ -16662,7 +16664,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="205" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="205" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="6"/>
       <c r="B205" s="18"/>
       <c r="C205" s="6">
@@ -16718,7 +16720,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="206" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="206" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="6"/>
       <c r="B206" s="18"/>
       <c r="C206" s="6">
@@ -16774,7 +16776,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="207" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="207" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="6"/>
       <c r="B207" s="18"/>
       <c r="C207" s="6">
@@ -16830,7 +16832,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="208" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="208" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="6"/>
       <c r="B208" s="18"/>
       <c r="C208" s="6">
@@ -16886,7 +16888,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="209" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="209" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="6"/>
       <c r="B209" s="18"/>
       <c r="C209" s="6">
@@ -16942,7 +16944,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="210" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="210" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="6"/>
       <c r="B210" s="18"/>
       <c r="C210" s="6">
@@ -16998,7 +17000,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="211" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="211" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="6"/>
       <c r="B211" s="18"/>
       <c r="C211" s="6">
@@ -17052,7 +17054,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="212" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="212" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="6"/>
       <c r="B212" s="18"/>
       <c r="C212" s="6">
@@ -17100,7 +17102,7 @@
       <c r="W212" s="6"/>
       <c r="X212" s="7"/>
     </row>
-    <row r="213" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="213" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="6"/>
       <c r="B213" s="18"/>
       <c r="C213" s="6">
@@ -17148,7 +17150,7 @@
       <c r="W213" s="6"/>
       <c r="X213" s="7"/>
     </row>
-    <row r="214" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="214" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="6"/>
       <c r="B214" s="18"/>
       <c r="C214" s="6">
@@ -17196,7 +17198,7 @@
       <c r="W214" s="6"/>
       <c r="X214" s="7"/>
     </row>
-    <row r="215" spans="1:24" ht="33" customHeight="1">
+    <row r="215" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="6" t="s">
         <v>1131</v>
       </c>
@@ -17254,7 +17256,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="216" spans="1:24" ht="33" customHeight="1">
+    <row r="216" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="6" t="s">
         <v>1131</v>
       </c>
@@ -17312,7 +17314,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="217" spans="1:24" ht="60">
+    <row r="217" spans="1:24" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A217" s="6" t="s">
         <v>1131</v>
       </c>
@@ -17366,7 +17368,7 @@
       <c r="W217" s="6"/>
       <c r="X217" s="7"/>
     </row>
-    <row r="218" spans="1:24" ht="120">
+    <row r="218" spans="1:24" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A218" s="6" t="s">
         <v>1205</v>
       </c>
@@ -17426,7 +17428,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="219" spans="1:24" ht="114.75" hidden="1" customHeight="1">
+    <row r="219" spans="1:24" ht="114.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="6" t="s">
         <v>1131</v>
       </c>
@@ -17476,7 +17478,7 @@
       </c>
       <c r="X219" s="7"/>
     </row>
-    <row r="220" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="220" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="6"/>
       <c r="B220" s="18"/>
       <c r="C220" s="6">
@@ -17526,7 +17528,7 @@
       <c r="W220" s="6"/>
       <c r="X220" s="7"/>
     </row>
-    <row r="221" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="221" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="6"/>
       <c r="B221" s="18"/>
       <c r="C221" s="6">
@@ -17574,7 +17576,7 @@
       </c>
       <c r="X221" s="7"/>
     </row>
-    <row r="222" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="222" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="6"/>
       <c r="B222" s="18"/>
       <c r="C222" s="6">
@@ -17624,7 +17626,7 @@
       <c r="W222" s="6"/>
       <c r="X222" s="7"/>
     </row>
-    <row r="223" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="223" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="6"/>
       <c r="B223" s="18"/>
       <c r="C223" s="6">
@@ -17672,7 +17674,7 @@
       </c>
       <c r="X223" s="7"/>
     </row>
-    <row r="224" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="224" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="6"/>
       <c r="B224" s="18"/>
       <c r="C224" s="6">
@@ -17722,7 +17724,7 @@
       <c r="W224" s="6"/>
       <c r="X224" s="7"/>
     </row>
-    <row r="225" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="225" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="6"/>
       <c r="B225" s="18"/>
       <c r="C225" s="6">
@@ -17770,7 +17772,7 @@
       </c>
       <c r="X225" s="7"/>
     </row>
-    <row r="226" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="226" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="6"/>
       <c r="B226" s="18"/>
       <c r="C226" s="6">
@@ -17818,7 +17820,7 @@
       <c r="W226" s="6"/>
       <c r="X226" s="7"/>
     </row>
-    <row r="227" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="227" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="6"/>
       <c r="B227" s="18"/>
       <c r="C227" s="6">
@@ -17876,7 +17878,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="228" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="228" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="6"/>
       <c r="B228" s="18"/>
       <c r="C228" s="6">
@@ -17934,7 +17936,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="229" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="229" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="6"/>
       <c r="B229" s="18"/>
       <c r="C229" s="6">
@@ -17988,7 +17990,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="230" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="230" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="6"/>
       <c r="B230" s="18"/>
       <c r="C230" s="6">
@@ -18038,7 +18040,7 @@
       <c r="W230" s="6"/>
       <c r="X230" s="7"/>
     </row>
-    <row r="231" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="231" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="6"/>
       <c r="B231" s="18"/>
       <c r="C231" s="6">
@@ -18086,7 +18088,7 @@
       </c>
       <c r="X231" s="7"/>
     </row>
-    <row r="232" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="232" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="6"/>
       <c r="B232" s="18"/>
       <c r="C232" s="6">
@@ -18142,7 +18144,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="233" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="233" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="6"/>
       <c r="B233" s="18"/>
       <c r="C233" s="6">
@@ -18192,7 +18194,7 @@
       <c r="W233" s="6"/>
       <c r="X233" s="7"/>
     </row>
-    <row r="234" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="234" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="6"/>
       <c r="B234" s="18"/>
       <c r="C234" s="6">
@@ -18240,7 +18242,7 @@
       </c>
       <c r="X234" s="7"/>
     </row>
-    <row r="235" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="235" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="6"/>
       <c r="B235" s="18"/>
       <c r="C235" s="6">
@@ -18296,7 +18298,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="236" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="236" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="6"/>
       <c r="B236" s="18"/>
       <c r="C236" s="6">
@@ -18346,7 +18348,7 @@
       <c r="W236" s="6"/>
       <c r="X236" s="7"/>
     </row>
-    <row r="237" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="237" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="6"/>
       <c r="B237" s="18"/>
       <c r="C237" s="6">
@@ -18394,7 +18396,7 @@
       </c>
       <c r="X237" s="7"/>
     </row>
-    <row r="238" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="238" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="6"/>
       <c r="B238" s="18"/>
       <c r="C238" s="6">
@@ -18450,7 +18452,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="239" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="239" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="6"/>
       <c r="B239" s="18"/>
       <c r="C239" s="6">
@@ -18500,7 +18502,7 @@
       <c r="W239" s="6"/>
       <c r="X239" s="7"/>
     </row>
-    <row r="240" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="240" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="6"/>
       <c r="B240" s="18"/>
       <c r="C240" s="6">
@@ -18548,7 +18550,7 @@
       </c>
       <c r="X240" s="7"/>
     </row>
-    <row r="241" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="241" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="6"/>
       <c r="B241" s="18"/>
       <c r="C241" s="6">
@@ -18604,7 +18606,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="242" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="242" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="6"/>
       <c r="B242" s="18"/>
       <c r="C242" s="6">
@@ -18654,7 +18656,7 @@
       <c r="W242" s="6"/>
       <c r="X242" s="7"/>
     </row>
-    <row r="243" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="243" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="6"/>
       <c r="B243" s="18"/>
       <c r="C243" s="6">
@@ -18702,7 +18704,7 @@
       </c>
       <c r="X243" s="7"/>
     </row>
-    <row r="244" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="244" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="6"/>
       <c r="B244" s="18"/>
       <c r="C244" s="6">
@@ -18758,7 +18760,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="245" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="245" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="6"/>
       <c r="B245" s="18"/>
       <c r="C245" s="6">
@@ -18808,7 +18810,7 @@
       <c r="W245" s="6"/>
       <c r="X245" s="7"/>
     </row>
-    <row r="246" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="246" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="6"/>
       <c r="B246" s="18"/>
       <c r="C246" s="6">
@@ -18856,7 +18858,7 @@
       </c>
       <c r="X246" s="7"/>
     </row>
-    <row r="247" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="247" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="6"/>
       <c r="B247" s="18"/>
       <c r="C247" s="6">
@@ -18912,7 +18914,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="248" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="248" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="6"/>
       <c r="B248" s="18"/>
       <c r="C248" s="6">
@@ -18962,7 +18964,7 @@
       <c r="W248" s="6"/>
       <c r="X248" s="7"/>
     </row>
-    <row r="249" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="249" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="6"/>
       <c r="B249" s="18"/>
       <c r="C249" s="6">
@@ -19010,7 +19012,7 @@
       </c>
       <c r="X249" s="7"/>
     </row>
-    <row r="250" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="250" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="6"/>
       <c r="B250" s="18"/>
       <c r="C250" s="6">
@@ -19060,7 +19062,7 @@
       <c r="W250" s="6"/>
       <c r="X250" s="7"/>
     </row>
-    <row r="251" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="251" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="6"/>
       <c r="B251" s="18"/>
       <c r="C251" s="6">
@@ -19108,7 +19110,7 @@
       </c>
       <c r="X251" s="7"/>
     </row>
-    <row r="252" spans="1:24" ht="33" customHeight="1">
+    <row r="252" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="6" t="s">
         <v>1131</v>
       </c>
@@ -19166,7 +19168,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="253" spans="1:24" ht="33" customHeight="1">
+    <row r="253" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19218,7 +19220,7 @@
       <c r="W253" s="6"/>
       <c r="X253" s="7"/>
     </row>
-    <row r="254" spans="1:24" ht="33" customHeight="1">
+    <row r="254" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19270,7 +19272,7 @@
       <c r="W254" s="6"/>
       <c r="X254" s="7"/>
     </row>
-    <row r="255" spans="1:24" ht="33" customHeight="1">
+    <row r="255" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="18"/>
       <c r="B255" s="6" t="s">
         <v>1196</v>
@@ -19328,7 +19330,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="256" spans="1:24" ht="33" customHeight="1">
+    <row r="256" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="6" t="s">
         <v>1131</v>
       </c>
@@ -19386,7 +19388,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="257" spans="1:24" ht="33" customHeight="1">
+    <row r="257" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19438,7 +19440,7 @@
       <c r="W257" s="6"/>
       <c r="X257" s="7"/>
     </row>
-    <row r="258" spans="1:24" ht="33" customHeight="1">
+    <row r="258" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19490,7 +19492,7 @@
       <c r="W258" s="6"/>
       <c r="X258" s="7"/>
     </row>
-    <row r="259" spans="1:24" ht="33" customHeight="1">
+    <row r="259" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="18"/>
       <c r="B259" s="6" t="s">
         <v>1196</v>
@@ -19548,7 +19550,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="260" spans="1:24" ht="33" customHeight="1">
+    <row r="260" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="6" t="s">
         <v>1131</v>
       </c>
@@ -19606,7 +19608,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="261" spans="1:24" ht="33" customHeight="1">
+    <row r="261" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19658,7 +19660,7 @@
       <c r="W261" s="6"/>
       <c r="X261" s="7"/>
     </row>
-    <row r="262" spans="1:24" ht="33" customHeight="1">
+    <row r="262" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19710,7 +19712,7 @@
       <c r="W262" s="6"/>
       <c r="X262" s="7"/>
     </row>
-    <row r="263" spans="1:24" ht="33" customHeight="1">
+    <row r="263" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="18"/>
       <c r="B263" s="6" t="s">
         <v>1196</v>
@@ -19768,7 +19770,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="264" spans="1:24" ht="33" customHeight="1">
+    <row r="264" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19826,7 +19828,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="265" spans="1:24" ht="33" customHeight="1">
+    <row r="265" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19884,7 +19886,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="266" spans="1:24" ht="33" customHeight="1">
+    <row r="266" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="6" t="s">
         <v>1196</v>
       </c>
@@ -19942,7 +19944,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="267" spans="1:24" ht="33" customHeight="1">
+    <row r="267" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20000,7 +20002,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="268" spans="1:24" ht="60">
+    <row r="268" spans="1:24" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A268" s="6" t="s">
         <v>1131</v>
       </c>
@@ -20058,7 +20060,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="269" spans="1:24" ht="33" customHeight="1">
+    <row r="269" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20116,7 +20118,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="270" spans="1:24" ht="33" customHeight="1">
+    <row r="270" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20174,7 +20176,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="271" spans="1:24" ht="33" customHeight="1">
+    <row r="271" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20232,7 +20234,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="272" spans="1:24" ht="33" customHeight="1">
+    <row r="272" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20290,7 +20292,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="273" spans="1:24" ht="33" customHeight="1">
+    <row r="273" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20350,7 +20352,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="274" spans="1:24" ht="33" customHeight="1">
+    <row r="274" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20408,7 +20410,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="275" spans="1:24" ht="33" customHeight="1">
+    <row r="275" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20466,7 +20468,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="276" spans="1:24" ht="33" customHeight="1">
+    <row r="276" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20526,7 +20528,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="277" spans="1:24" ht="33" customHeight="1">
+    <row r="277" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20584,7 +20586,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="278" spans="1:24" ht="80">
+    <row r="278" spans="1:24" ht="75" x14ac:dyDescent="0.4">
       <c r="A278" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20642,7 +20644,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="279" spans="1:24" ht="60">
+    <row r="279" spans="1:24" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A279" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20700,7 +20702,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="280" spans="1:24" ht="33" customHeight="1">
+    <row r="280" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20758,7 +20760,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="281" spans="1:24" ht="77.25" customHeight="1">
+    <row r="281" spans="1:24" ht="77.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20816,7 +20818,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="282" spans="1:24" ht="33" customHeight="1">
+    <row r="282" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="6" t="s">
         <v>1196</v>
       </c>
@@ -20876,7 +20878,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="283" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="283" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="6"/>
       <c r="B283" s="18"/>
       <c r="C283" s="6">
@@ -20930,7 +20932,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="284" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="284" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="6"/>
       <c r="B284" s="18"/>
       <c r="C284" s="6">
@@ -20984,7 +20986,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="285" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="285" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="6"/>
       <c r="B285" s="18"/>
       <c r="C285" s="6">
@@ -21038,7 +21040,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="286" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="286" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="6"/>
       <c r="B286" s="18"/>
       <c r="C286" s="6">
@@ -21092,7 +21094,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="287" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="287" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="6"/>
       <c r="B287" s="18"/>
       <c r="C287" s="6">
@@ -21146,7 +21148,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="288" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="288" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="6"/>
       <c r="B288" s="18"/>
       <c r="C288" s="6">
@@ -21200,7 +21202,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="289" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="289" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="6"/>
       <c r="B289" s="18"/>
       <c r="C289" s="6">
@@ -21254,7 +21256,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="290" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="290" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="6"/>
       <c r="B290" s="18"/>
       <c r="C290" s="6">
@@ -21308,7 +21310,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="291" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="291" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="6"/>
       <c r="B291" s="18"/>
       <c r="C291" s="6">
@@ -21362,7 +21364,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="292" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="292" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="6"/>
       <c r="B292" s="18"/>
       <c r="C292" s="6">
@@ -21416,7 +21418,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="293" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="293" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="6"/>
       <c r="B293" s="18"/>
       <c r="C293" s="6">
@@ -21470,7 +21472,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="294" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="294" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="6"/>
       <c r="B294" s="18"/>
       <c r="C294" s="6">
@@ -21526,7 +21528,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="295" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="295" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="6"/>
       <c r="B295" s="18"/>
       <c r="C295" s="6">
@@ -21580,7 +21582,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="296" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="296" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="6"/>
       <c r="B296" s="18"/>
       <c r="C296" s="6">
@@ -21634,7 +21636,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="297" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="297" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="6"/>
       <c r="B297" s="18"/>
       <c r="C297" s="6">
@@ -21688,7 +21690,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="298" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="298" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="6"/>
       <c r="B298" s="18"/>
       <c r="C298" s="6">
@@ -21742,7 +21744,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="299" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="299" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="6"/>
       <c r="B299" s="18"/>
       <c r="C299" s="6">
@@ -21796,7 +21798,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="300" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="300" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="6"/>
       <c r="B300" s="18"/>
       <c r="C300" s="6">
@@ -21850,7 +21852,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="301" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="301" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="6"/>
       <c r="B301" s="18"/>
       <c r="C301" s="6">
@@ -21904,7 +21906,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="302" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="302" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="6"/>
       <c r="B302" s="18"/>
       <c r="C302" s="6">
@@ -21958,7 +21960,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="303" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="303" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="6"/>
       <c r="B303" s="18"/>
       <c r="C303" s="6">
@@ -22012,7 +22014,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="304" spans="1:24" ht="33" hidden="1" customHeight="1">
+    <row r="304" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="6"/>
       <c r="B304" s="18"/>
       <c r="C304" s="6">
@@ -22066,7 +22068,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="33" hidden="1" customHeight="1">
+    <row r="305" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="6"/>
       <c r="B305" s="18"/>
       <c r="C305" s="6">
@@ -22120,7 +22122,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="33" hidden="1" customHeight="1">
+    <row r="306" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="6"/>
       <c r="B306" s="18"/>
       <c r="C306" s="6">
@@ -22174,7 +22176,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="33" hidden="1" customHeight="1">
+    <row r="307" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="6"/>
       <c r="B307" s="18"/>
       <c r="C307" s="6">
@@ -22228,7 +22230,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="99.75" customHeight="1">
+    <row r="308" spans="1:25" ht="99.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="6"/>
       <c r="B308" s="6" t="s">
         <v>1196</v>
@@ -22286,7 +22288,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="117" customHeight="1">
+    <row r="309" spans="1:25" ht="117" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="6"/>
       <c r="B309" s="6" t="s">
         <v>1196</v>
@@ -22344,7 +22346,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="60" hidden="1">
+    <row r="310" spans="1:25" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A310" s="6"/>
       <c r="B310" s="18"/>
       <c r="C310" s="6">
@@ -22401,7 +22403,7 @@
       </c>
       <c r="Y310"/>
     </row>
-    <row r="311" spans="1:25" ht="40" hidden="1">
+    <row r="311" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A311" s="6"/>
       <c r="B311" s="18"/>
       <c r="C311" s="6">
@@ -22458,7 +22460,7 @@
       </c>
       <c r="Y311"/>
     </row>
-    <row r="312" spans="1:25" ht="40" hidden="1">
+    <row r="312" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A312" s="6"/>
       <c r="B312" s="18"/>
       <c r="C312" s="6">
@@ -22515,7 +22517,7 @@
       </c>
       <c r="Y312"/>
     </row>
-    <row r="313" spans="1:25" ht="60" hidden="1">
+    <row r="313" spans="1:25" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A313" s="6"/>
       <c r="B313" s="18"/>
       <c r="C313" s="6">
@@ -22572,7 +22574,7 @@
       </c>
       <c r="Y313"/>
     </row>
-    <row r="314" spans="1:25" ht="40" hidden="1">
+    <row r="314" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A314" s="6"/>
       <c r="B314" s="18"/>
       <c r="C314" s="6">
@@ -22629,7 +22631,7 @@
       </c>
       <c r="Y314"/>
     </row>
-    <row r="315" spans="1:25" ht="40" hidden="1">
+    <row r="315" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A315" s="6"/>
       <c r="B315" s="18"/>
       <c r="C315" s="6">
@@ -22686,7 +22688,7 @@
       </c>
       <c r="Y315"/>
     </row>
-    <row r="316" spans="1:25" ht="40" hidden="1">
+    <row r="316" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A316" s="6"/>
       <c r="B316" s="18"/>
       <c r="C316" s="6">
@@ -22743,7 +22745,7 @@
       </c>
       <c r="Y316"/>
     </row>
-    <row r="317" spans="1:25" ht="40" hidden="1">
+    <row r="317" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A317" s="6"/>
       <c r="B317" s="18"/>
       <c r="C317" s="6">
@@ -22800,7 +22802,7 @@
       </c>
       <c r="Y317"/>
     </row>
-    <row r="318" spans="1:25" ht="40" hidden="1">
+    <row r="318" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A318" s="6"/>
       <c r="B318" s="18"/>
       <c r="C318" s="6">
@@ -22857,7 +22859,7 @@
       </c>
       <c r="Y318"/>
     </row>
-    <row r="319" spans="1:25" ht="60" hidden="1">
+    <row r="319" spans="1:25" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A319" s="6"/>
       <c r="B319" s="18"/>
       <c r="C319" s="6">
@@ -22914,7 +22916,7 @@
       </c>
       <c r="Y319"/>
     </row>
-    <row r="320" spans="1:25" ht="40" hidden="1">
+    <row r="320" spans="1:25" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A320" s="6"/>
       <c r="B320" s="18"/>
       <c r="C320" s="6">
@@ -22971,7 +22973,7 @@
       </c>
       <c r="Y320"/>
     </row>
-    <row r="321" spans="1:26" ht="40" hidden="1">
+    <row r="321" spans="1:26" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A321" s="6"/>
       <c r="B321" s="18"/>
       <c r="C321" s="6">
@@ -23028,7 +23030,7 @@
       </c>
       <c r="Y321"/>
     </row>
-    <row r="322" spans="1:26" ht="40" hidden="1">
+    <row r="322" spans="1:26" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A322" s="6"/>
       <c r="B322" s="18"/>
       <c r="C322" s="6">
@@ -23085,7 +23087,7 @@
       </c>
       <c r="Y322"/>
     </row>
-    <row r="323" spans="1:26" ht="40" hidden="1">
+    <row r="323" spans="1:26" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A323" s="6"/>
       <c r="B323" s="18"/>
       <c r="C323" s="6">
@@ -23142,7 +23144,7 @@
       </c>
       <c r="Y323"/>
     </row>
-    <row r="324" spans="1:26" ht="40" hidden="1">
+    <row r="324" spans="1:26" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A324" s="6"/>
       <c r="B324" s="18"/>
       <c r="C324" s="6">
@@ -23199,7 +23201,7 @@
       </c>
       <c r="Y324"/>
     </row>
-    <row r="325" spans="1:26" ht="20" hidden="1">
+    <row r="325" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A325" s="19" t="s">
         <v>1225</v>
       </c>
@@ -23231,7 +23233,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" spans="1:26" ht="20" hidden="1">
+    <row r="326" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A326" s="19" t="s">
         <v>1223</v>
       </c>
@@ -23263,7 +23265,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" spans="1:26" ht="20" hidden="1">
+    <row r="327" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A327" s="19" t="s">
         <v>1238</v>
       </c>
@@ -23295,7 +23297,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" spans="1:26" ht="20" hidden="1">
+    <row r="328" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A328" s="19" t="s">
         <v>1224</v>
       </c>
@@ -23327,7 +23329,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" spans="1:26" ht="20" hidden="1">
+    <row r="329" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A329" s="19" t="s">
         <v>1247</v>
       </c>
@@ -23359,7 +23361,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="1:26" ht="20" hidden="1">
+    <row r="330" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A330" s="19" t="s">
         <v>1197</v>
       </c>
@@ -23391,7 +23393,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="1:26" ht="20" hidden="1">
+    <row r="331" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A331" s="1" t="s">
         <v>1198</v>
       </c>
@@ -23401,42 +23403,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X331" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:X331" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="44">
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="X88:X89"/>
-    <mergeCell ref="X90:X91"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B84:B87"/>
     <mergeCell ref="X37:X39"/>
     <mergeCell ref="X34:X36"/>
     <mergeCell ref="A62:A63"/>
@@ -23453,6 +23421,34 @@
     <mergeCell ref="B80:B83"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="X88:X89"/>
+    <mergeCell ref="X90:X91"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A58"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.19685039370078741"/>
